--- a/data-raw/bmw_qtrly_benchmarks_2025.xlsx
+++ b/data-raw/bmw_qtrly_benchmarks_2025.xlsx
@@ -10,12 +10,14 @@
     <sheet name="bmw_femaleq" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="bmw_aapiq" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="bmw_zmq" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="bmw_millennialq" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="bmw_genzq" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="56">
   <si>
     <t xml:space="preserve">quarter</t>
   </si>
@@ -174,6 +176,15 @@
   </si>
   <si>
     <t xml:space="preserve">Gen Z/Millennial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">generations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Millennials</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gen Z</t>
   </si>
 </sst>
 </file>
@@ -15190,4 +15201,7566 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B2" s="1" t="n">
+        <v>45658</v>
+      </c>
+      <c r="C2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.549206349206348</v>
+      </c>
+      <c r="E2" t="n">
+        <v>346</v>
+      </c>
+      <c r="F2" t="n">
+        <v>630</v>
+      </c>
+      <c r="G2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B3" s="1" t="n">
+        <v>45748</v>
+      </c>
+      <c r="C3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.590211833455061</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1616</v>
+      </c>
+      <c r="F3" t="n">
+        <v>2738</v>
+      </c>
+      <c r="G3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B4" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.601552393272969</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1860</v>
+      </c>
+      <c r="F4" t="n">
+        <v>3092</v>
+      </c>
+      <c r="G4" t="s">
+        <v>8</v>
+      </c>
+      <c r="H4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.59923920340122</v>
+      </c>
+      <c r="E5" t="n">
+        <v>2678</v>
+      </c>
+      <c r="F5" t="n">
+        <v>4469</v>
+      </c>
+      <c r="G5" t="s">
+        <v>8</v>
+      </c>
+      <c r="H5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B6" s="1" t="n">
+        <v>45658</v>
+      </c>
+      <c r="C6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.94285714285714</v>
+      </c>
+      <c r="E6" t="n">
+        <v>594</v>
+      </c>
+      <c r="F6" t="n">
+        <v>630</v>
+      </c>
+      <c r="G6" t="s">
+        <v>8</v>
+      </c>
+      <c r="H6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>54</v>
+      </c>
+      <c r="B7" s="1" t="n">
+        <v>45748</v>
+      </c>
+      <c r="C7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.933528122717284</v>
+      </c>
+      <c r="E7" t="n">
+        <v>2556</v>
+      </c>
+      <c r="F7" t="n">
+        <v>2738</v>
+      </c>
+      <c r="G7" t="s">
+        <v>8</v>
+      </c>
+      <c r="H7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>54</v>
+      </c>
+      <c r="B8" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.938874514877114</v>
+      </c>
+      <c r="E8" t="n">
+        <v>2903</v>
+      </c>
+      <c r="F8" t="n">
+        <v>3092</v>
+      </c>
+      <c r="G8" t="s">
+        <v>8</v>
+      </c>
+      <c r="H8" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>54</v>
+      </c>
+      <c r="B9" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C9" t="s">
+        <v>10</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.945849183262564</v>
+      </c>
+      <c r="E9" t="n">
+        <v>4227</v>
+      </c>
+      <c r="F9" t="n">
+        <v>4469</v>
+      </c>
+      <c r="G9" t="s">
+        <v>8</v>
+      </c>
+      <c r="H9" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>54</v>
+      </c>
+      <c r="B10" s="1" t="n">
+        <v>45658</v>
+      </c>
+      <c r="C10" t="s">
+        <v>11</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.542087542087542</v>
+      </c>
+      <c r="E10" t="n">
+        <v>322</v>
+      </c>
+      <c r="F10" t="n">
+        <v>594</v>
+      </c>
+      <c r="G10" t="s">
+        <v>8</v>
+      </c>
+      <c r="H10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>54</v>
+      </c>
+      <c r="B11" s="1" t="n">
+        <v>45748</v>
+      </c>
+      <c r="C11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.54303599374022</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1388</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2556</v>
+      </c>
+      <c r="G11" t="s">
+        <v>8</v>
+      </c>
+      <c r="H11" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>54</v>
+      </c>
+      <c r="B12" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C12" t="s">
+        <v>11</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.591112642094397</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1716</v>
+      </c>
+      <c r="F12" t="n">
+        <v>2903</v>
+      </c>
+      <c r="G12" t="s">
+        <v>8</v>
+      </c>
+      <c r="H12" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>54</v>
+      </c>
+      <c r="B13" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C13" t="s">
+        <v>11</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.56943458717767</v>
+      </c>
+      <c r="E13" t="n">
+        <v>2407</v>
+      </c>
+      <c r="F13" t="n">
+        <v>4227</v>
+      </c>
+      <c r="G13" t="s">
+        <v>8</v>
+      </c>
+      <c r="H13" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>54</v>
+      </c>
+      <c r="B14" s="1" t="n">
+        <v>45658</v>
+      </c>
+      <c r="C14" t="s">
+        <v>12</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.61784511784512</v>
+      </c>
+      <c r="E14" t="n">
+        <v>367</v>
+      </c>
+      <c r="F14" t="n">
+        <v>594</v>
+      </c>
+      <c r="G14" t="s">
+        <v>8</v>
+      </c>
+      <c r="H14" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>54</v>
+      </c>
+      <c r="B15" s="1" t="n">
+        <v>45748</v>
+      </c>
+      <c r="C15" t="s">
+        <v>12</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.573943661971828</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1467</v>
+      </c>
+      <c r="F15" t="n">
+        <v>2556</v>
+      </c>
+      <c r="G15" t="s">
+        <v>8</v>
+      </c>
+      <c r="H15" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>54</v>
+      </c>
+      <c r="B16" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C16" t="s">
+        <v>12</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.5818119187048</v>
+      </c>
+      <c r="E16" t="n">
+        <v>1689</v>
+      </c>
+      <c r="F16" t="n">
+        <v>2903</v>
+      </c>
+      <c r="G16" t="s">
+        <v>8</v>
+      </c>
+      <c r="H16" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>54</v>
+      </c>
+      <c r="B17" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C17" t="s">
+        <v>12</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.570617459190918</v>
+      </c>
+      <c r="E17" t="n">
+        <v>2412</v>
+      </c>
+      <c r="F17" t="n">
+        <v>4227</v>
+      </c>
+      <c r="G17" t="s">
+        <v>8</v>
+      </c>
+      <c r="H17" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>54</v>
+      </c>
+      <c r="B18" s="1" t="n">
+        <v>45658</v>
+      </c>
+      <c r="C18" t="s">
+        <v>13</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.422558922558921</v>
+      </c>
+      <c r="E18" t="n">
+        <v>251</v>
+      </c>
+      <c r="F18" t="n">
+        <v>594</v>
+      </c>
+      <c r="G18" t="s">
+        <v>8</v>
+      </c>
+      <c r="H18" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>54</v>
+      </c>
+      <c r="B19" s="1" t="n">
+        <v>45748</v>
+      </c>
+      <c r="C19" t="s">
+        <v>13</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.422143974960881</v>
+      </c>
+      <c r="E19" t="n">
+        <v>1079</v>
+      </c>
+      <c r="F19" t="n">
+        <v>2556</v>
+      </c>
+      <c r="G19" t="s">
+        <v>8</v>
+      </c>
+      <c r="H19" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>54</v>
+      </c>
+      <c r="B20" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C20" t="s">
+        <v>13</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.435756114364465</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1265</v>
+      </c>
+      <c r="F20" t="n">
+        <v>2903</v>
+      </c>
+      <c r="G20" t="s">
+        <v>8</v>
+      </c>
+      <c r="H20" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>54</v>
+      </c>
+      <c r="B21" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C21" t="s">
+        <v>13</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.419209841495142</v>
+      </c>
+      <c r="E21" t="n">
+        <v>1772</v>
+      </c>
+      <c r="F21" t="n">
+        <v>4227</v>
+      </c>
+      <c r="G21" t="s">
+        <v>8</v>
+      </c>
+      <c r="H21" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>54</v>
+      </c>
+      <c r="B22" s="1" t="n">
+        <v>45658</v>
+      </c>
+      <c r="C22" t="s">
+        <v>14</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0.658249158249161</v>
+      </c>
+      <c r="E22" t="n">
+        <v>391</v>
+      </c>
+      <c r="F22" t="n">
+        <v>594</v>
+      </c>
+      <c r="G22" t="s">
+        <v>8</v>
+      </c>
+      <c r="H22" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>54</v>
+      </c>
+      <c r="B23" s="1" t="n">
+        <v>45748</v>
+      </c>
+      <c r="C23" t="s">
+        <v>14</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0.652190923317671</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1667</v>
+      </c>
+      <c r="F23" t="n">
+        <v>2556</v>
+      </c>
+      <c r="G23" t="s">
+        <v>8</v>
+      </c>
+      <c r="H23" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>54</v>
+      </c>
+      <c r="B24" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C24" t="s">
+        <v>14</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0.682741991043752</v>
+      </c>
+      <c r="E24" t="n">
+        <v>1982</v>
+      </c>
+      <c r="F24" t="n">
+        <v>2903</v>
+      </c>
+      <c r="G24" t="s">
+        <v>8</v>
+      </c>
+      <c r="H24" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>54</v>
+      </c>
+      <c r="B25" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C25" t="s">
+        <v>14</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0.651762479299759</v>
+      </c>
+      <c r="E25" t="n">
+        <v>2755</v>
+      </c>
+      <c r="F25" t="n">
+        <v>4227</v>
+      </c>
+      <c r="G25" t="s">
+        <v>8</v>
+      </c>
+      <c r="H25" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>54</v>
+      </c>
+      <c r="B26" s="1" t="n">
+        <v>45658</v>
+      </c>
+      <c r="C26" t="s">
+        <v>15</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0.488215488215487</v>
+      </c>
+      <c r="E26" t="n">
+        <v>290</v>
+      </c>
+      <c r="F26" t="n">
+        <v>594</v>
+      </c>
+      <c r="G26" t="s">
+        <v>16</v>
+      </c>
+      <c r="H26" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>54</v>
+      </c>
+      <c r="B27" s="1" t="n">
+        <v>45748</v>
+      </c>
+      <c r="C27" t="s">
+        <v>15</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0.478873239436626</v>
+      </c>
+      <c r="E27" t="n">
+        <v>1224</v>
+      </c>
+      <c r="F27" t="n">
+        <v>2556</v>
+      </c>
+      <c r="G27" t="s">
+        <v>16</v>
+      </c>
+      <c r="H27" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>54</v>
+      </c>
+      <c r="B28" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C28" t="s">
+        <v>15</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0.496038580778524</v>
+      </c>
+      <c r="E28" t="n">
+        <v>1440</v>
+      </c>
+      <c r="F28" t="n">
+        <v>2903</v>
+      </c>
+      <c r="G28" t="s">
+        <v>16</v>
+      </c>
+      <c r="H28" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>54</v>
+      </c>
+      <c r="B29" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C29" t="s">
+        <v>15</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0.472202507688658</v>
+      </c>
+      <c r="E29" t="n">
+        <v>1996</v>
+      </c>
+      <c r="F29" t="n">
+        <v>4227</v>
+      </c>
+      <c r="G29" t="s">
+        <v>16</v>
+      </c>
+      <c r="H29" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s">
+        <v>54</v>
+      </c>
+      <c r="B30" s="1" t="n">
+        <v>45658</v>
+      </c>
+      <c r="C30" t="s">
+        <v>17</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0.319865319865319</v>
+      </c>
+      <c r="E30" t="n">
+        <v>190</v>
+      </c>
+      <c r="F30" t="n">
+        <v>594</v>
+      </c>
+      <c r="G30" t="s">
+        <v>16</v>
+      </c>
+      <c r="H30" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s">
+        <v>54</v>
+      </c>
+      <c r="B31" s="1" t="n">
+        <v>45748</v>
+      </c>
+      <c r="C31" t="s">
+        <v>17</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0.365023474178408</v>
+      </c>
+      <c r="E31" t="n">
+        <v>933</v>
+      </c>
+      <c r="F31" t="n">
+        <v>2556</v>
+      </c>
+      <c r="G31" t="s">
+        <v>16</v>
+      </c>
+      <c r="H31" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s">
+        <v>54</v>
+      </c>
+      <c r="B32" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C32" t="s">
+        <v>17</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0.370306579400629</v>
+      </c>
+      <c r="E32" t="n">
+        <v>1075</v>
+      </c>
+      <c r="F32" t="n">
+        <v>2903</v>
+      </c>
+      <c r="G32" t="s">
+        <v>16</v>
+      </c>
+      <c r="H32" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s">
+        <v>54</v>
+      </c>
+      <c r="B33" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C33" t="s">
+        <v>17</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0.365744026496326</v>
+      </c>
+      <c r="E33" t="n">
+        <v>1546</v>
+      </c>
+      <c r="F33" t="n">
+        <v>4227</v>
+      </c>
+      <c r="G33" t="s">
+        <v>16</v>
+      </c>
+      <c r="H33" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s">
+        <v>54</v>
+      </c>
+      <c r="B34" s="1" t="n">
+        <v>45658</v>
+      </c>
+      <c r="C34" t="s">
+        <v>18</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0.276094276094276</v>
+      </c>
+      <c r="E34" t="n">
+        <v>164</v>
+      </c>
+      <c r="F34" t="n">
+        <v>594</v>
+      </c>
+      <c r="G34" t="s">
+        <v>16</v>
+      </c>
+      <c r="H34" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s">
+        <v>54</v>
+      </c>
+      <c r="B35" s="1" t="n">
+        <v>45748</v>
+      </c>
+      <c r="C35" t="s">
+        <v>18</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0.298513302034432</v>
+      </c>
+      <c r="E35" t="n">
+        <v>763</v>
+      </c>
+      <c r="F35" t="n">
+        <v>2556</v>
+      </c>
+      <c r="G35" t="s">
+        <v>16</v>
+      </c>
+      <c r="H35" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s">
+        <v>54</v>
+      </c>
+      <c r="B36" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C36" t="s">
+        <v>18</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0.334826042025497</v>
+      </c>
+      <c r="E36" t="n">
+        <v>972</v>
+      </c>
+      <c r="F36" t="n">
+        <v>2903</v>
+      </c>
+      <c r="G36" t="s">
+        <v>16</v>
+      </c>
+      <c r="H36" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s">
+        <v>54</v>
+      </c>
+      <c r="B37" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C37" t="s">
+        <v>18</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0.317009699550503</v>
+      </c>
+      <c r="E37" t="n">
+        <v>1340</v>
+      </c>
+      <c r="F37" t="n">
+        <v>4227</v>
+      </c>
+      <c r="G37" t="s">
+        <v>16</v>
+      </c>
+      <c r="H37" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s">
+        <v>54</v>
+      </c>
+      <c r="B38" s="1" t="n">
+        <v>45658</v>
+      </c>
+      <c r="C38" t="s">
+        <v>19</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0.612794612794614</v>
+      </c>
+      <c r="E38" t="n">
+        <v>364</v>
+      </c>
+      <c r="F38" t="n">
+        <v>594</v>
+      </c>
+      <c r="G38" t="s">
+        <v>16</v>
+      </c>
+      <c r="H38" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s">
+        <v>54</v>
+      </c>
+      <c r="B39" s="1" t="n">
+        <v>45748</v>
+      </c>
+      <c r="C39" t="s">
+        <v>19</v>
+      </c>
+      <c r="D39" t="n">
+        <v>0.621283255086063</v>
+      </c>
+      <c r="E39" t="n">
+        <v>1588</v>
+      </c>
+      <c r="F39" t="n">
+        <v>2556</v>
+      </c>
+      <c r="G39" t="s">
+        <v>16</v>
+      </c>
+      <c r="H39" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s">
+        <v>54</v>
+      </c>
+      <c r="B40" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C40" t="s">
+        <v>19</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0.653806407165008</v>
+      </c>
+      <c r="E40" t="n">
+        <v>1898</v>
+      </c>
+      <c r="F40" t="n">
+        <v>2903</v>
+      </c>
+      <c r="G40" t="s">
+        <v>16</v>
+      </c>
+      <c r="H40" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s">
+        <v>54</v>
+      </c>
+      <c r="B41" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C41" t="s">
+        <v>19</v>
+      </c>
+      <c r="D41" t="n">
+        <v>0.617459190915555</v>
+      </c>
+      <c r="E41" t="n">
+        <v>2610</v>
+      </c>
+      <c r="F41" t="n">
+        <v>4227</v>
+      </c>
+      <c r="G41" t="s">
+        <v>16</v>
+      </c>
+      <c r="H41" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s">
+        <v>54</v>
+      </c>
+      <c r="B42" s="1" t="n">
+        <v>45658</v>
+      </c>
+      <c r="C42" t="s">
+        <v>20</v>
+      </c>
+      <c r="D42" t="n">
+        <v>0.478114478114477</v>
+      </c>
+      <c r="E42" t="n">
+        <v>284</v>
+      </c>
+      <c r="F42" t="n">
+        <v>594</v>
+      </c>
+      <c r="G42" t="s">
+        <v>16</v>
+      </c>
+      <c r="H42" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s">
+        <v>54</v>
+      </c>
+      <c r="B43" s="1" t="n">
+        <v>45748</v>
+      </c>
+      <c r="C43" t="s">
+        <v>20</v>
+      </c>
+      <c r="D43" t="n">
+        <v>0.468701095461665</v>
+      </c>
+      <c r="E43" t="n">
+        <v>1198</v>
+      </c>
+      <c r="F43" t="n">
+        <v>2556</v>
+      </c>
+      <c r="G43" t="s">
+        <v>16</v>
+      </c>
+      <c r="H43" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s">
+        <v>54</v>
+      </c>
+      <c r="B44" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C44" t="s">
+        <v>20</v>
+      </c>
+      <c r="D44" t="n">
+        <v>0.493971753358613</v>
+      </c>
+      <c r="E44" t="n">
+        <v>1434</v>
+      </c>
+      <c r="F44" t="n">
+        <v>2903</v>
+      </c>
+      <c r="G44" t="s">
+        <v>16</v>
+      </c>
+      <c r="H44" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s">
+        <v>54</v>
+      </c>
+      <c r="B45" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C45" t="s">
+        <v>20</v>
+      </c>
+      <c r="D45" t="n">
+        <v>0.481428909391993</v>
+      </c>
+      <c r="E45" t="n">
+        <v>2035</v>
+      </c>
+      <c r="F45" t="n">
+        <v>4227</v>
+      </c>
+      <c r="G45" t="s">
+        <v>16</v>
+      </c>
+      <c r="H45" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s">
+        <v>54</v>
+      </c>
+      <c r="B46" s="1" t="n">
+        <v>45658</v>
+      </c>
+      <c r="C46" t="s">
+        <v>21</v>
+      </c>
+      <c r="D46" t="n">
+        <v>0.55050505050505</v>
+      </c>
+      <c r="E46" t="n">
+        <v>327</v>
+      </c>
+      <c r="F46" t="n">
+        <v>594</v>
+      </c>
+      <c r="G46" t="s">
+        <v>16</v>
+      </c>
+      <c r="H46" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s">
+        <v>54</v>
+      </c>
+      <c r="B47" s="1" t="n">
+        <v>45748</v>
+      </c>
+      <c r="C47" t="s">
+        <v>21</v>
+      </c>
+      <c r="D47" t="n">
+        <v>0.546165884194053</v>
+      </c>
+      <c r="E47" t="n">
+        <v>1396</v>
+      </c>
+      <c r="F47" t="n">
+        <v>2556</v>
+      </c>
+      <c r="G47" t="s">
+        <v>16</v>
+      </c>
+      <c r="H47" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s">
+        <v>54</v>
+      </c>
+      <c r="B48" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C48" t="s">
+        <v>21</v>
+      </c>
+      <c r="D48" t="n">
+        <v>0.581122976231497</v>
+      </c>
+      <c r="E48" t="n">
+        <v>1687</v>
+      </c>
+      <c r="F48" t="n">
+        <v>2903</v>
+      </c>
+      <c r="G48" t="s">
+        <v>16</v>
+      </c>
+      <c r="H48" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s">
+        <v>54</v>
+      </c>
+      <c r="B49" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C49" t="s">
+        <v>21</v>
+      </c>
+      <c r="D49" t="n">
+        <v>0.543647977288855</v>
+      </c>
+      <c r="E49" t="n">
+        <v>2298</v>
+      </c>
+      <c r="F49" t="n">
+        <v>4227</v>
+      </c>
+      <c r="G49" t="s">
+        <v>16</v>
+      </c>
+      <c r="H49" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s">
+        <v>54</v>
+      </c>
+      <c r="B50" s="1" t="n">
+        <v>45658</v>
+      </c>
+      <c r="C50" t="s">
+        <v>22</v>
+      </c>
+      <c r="D50" t="n">
+        <v>0.476430976430975</v>
+      </c>
+      <c r="E50" t="n">
+        <v>283</v>
+      </c>
+      <c r="F50" t="n">
+        <v>594</v>
+      </c>
+      <c r="G50" t="s">
+        <v>16</v>
+      </c>
+      <c r="H50" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s">
+        <v>54</v>
+      </c>
+      <c r="B51" s="1" t="n">
+        <v>45748</v>
+      </c>
+      <c r="C51" t="s">
+        <v>22</v>
+      </c>
+      <c r="D51" t="n">
+        <v>0.480829420970272</v>
+      </c>
+      <c r="E51" t="n">
+        <v>1229</v>
+      </c>
+      <c r="F51" t="n">
+        <v>2556</v>
+      </c>
+      <c r="G51" t="s">
+        <v>16</v>
+      </c>
+      <c r="H51" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s">
+        <v>54</v>
+      </c>
+      <c r="B52" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C52" t="s">
+        <v>22</v>
+      </c>
+      <c r="D52" t="n">
+        <v>0.515673441267672</v>
+      </c>
+      <c r="E52" t="n">
+        <v>1497</v>
+      </c>
+      <c r="F52" t="n">
+        <v>2903</v>
+      </c>
+      <c r="G52" t="s">
+        <v>16</v>
+      </c>
+      <c r="H52" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s">
+        <v>54</v>
+      </c>
+      <c r="B53" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C53" t="s">
+        <v>22</v>
+      </c>
+      <c r="D53" t="n">
+        <v>0.470073338064811</v>
+      </c>
+      <c r="E53" t="n">
+        <v>1987</v>
+      </c>
+      <c r="F53" t="n">
+        <v>4227</v>
+      </c>
+      <c r="G53" t="s">
+        <v>16</v>
+      </c>
+      <c r="H53" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s">
+        <v>54</v>
+      </c>
+      <c r="B54" s="1" t="n">
+        <v>45658</v>
+      </c>
+      <c r="C54" t="s">
+        <v>23</v>
+      </c>
+      <c r="D54" t="n">
+        <v>0.483164983164982</v>
+      </c>
+      <c r="E54" t="n">
+        <v>287</v>
+      </c>
+      <c r="F54" t="n">
+        <v>594</v>
+      </c>
+      <c r="G54" t="s">
+        <v>16</v>
+      </c>
+      <c r="H54" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s">
+        <v>54</v>
+      </c>
+      <c r="B55" s="1" t="n">
+        <v>45748</v>
+      </c>
+      <c r="C55" t="s">
+        <v>23</v>
+      </c>
+      <c r="D55" t="n">
+        <v>0.490610328638504</v>
+      </c>
+      <c r="E55" t="n">
+        <v>1254</v>
+      </c>
+      <c r="F55" t="n">
+        <v>2556</v>
+      </c>
+      <c r="G55" t="s">
+        <v>16</v>
+      </c>
+      <c r="H55" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s">
+        <v>54</v>
+      </c>
+      <c r="B56" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C56" t="s">
+        <v>23</v>
+      </c>
+      <c r="D56" t="n">
+        <v>0.533930416810213</v>
+      </c>
+      <c r="E56" t="n">
+        <v>1550</v>
+      </c>
+      <c r="F56" t="n">
+        <v>2903</v>
+      </c>
+      <c r="G56" t="s">
+        <v>16</v>
+      </c>
+      <c r="H56" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s">
+        <v>54</v>
+      </c>
+      <c r="B57" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C57" t="s">
+        <v>23</v>
+      </c>
+      <c r="D57" t="n">
+        <v>0.501064584811912</v>
+      </c>
+      <c r="E57" t="n">
+        <v>2118</v>
+      </c>
+      <c r="F57" t="n">
+        <v>4227</v>
+      </c>
+      <c r="G57" t="s">
+        <v>16</v>
+      </c>
+      <c r="H57" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s">
+        <v>54</v>
+      </c>
+      <c r="B58" s="1" t="n">
+        <v>45658</v>
+      </c>
+      <c r="C58" t="s">
+        <v>24</v>
+      </c>
+      <c r="D58" t="n">
+        <v>0.405723905723905</v>
+      </c>
+      <c r="E58" t="n">
+        <v>241</v>
+      </c>
+      <c r="F58" t="n">
+        <v>594</v>
+      </c>
+      <c r="G58" t="s">
+        <v>16</v>
+      </c>
+      <c r="H58" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s">
+        <v>54</v>
+      </c>
+      <c r="B59" s="1" t="n">
+        <v>45748</v>
+      </c>
+      <c r="C59" t="s">
+        <v>24</v>
+      </c>
+      <c r="D59" t="n">
+        <v>0.422143974960881</v>
+      </c>
+      <c r="E59" t="n">
+        <v>1079</v>
+      </c>
+      <c r="F59" t="n">
+        <v>2556</v>
+      </c>
+      <c r="G59" t="s">
+        <v>16</v>
+      </c>
+      <c r="H59" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s">
+        <v>54</v>
+      </c>
+      <c r="B60" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C60" t="s">
+        <v>24</v>
+      </c>
+      <c r="D60" t="n">
+        <v>0.445401308990714</v>
+      </c>
+      <c r="E60" t="n">
+        <v>1293</v>
+      </c>
+      <c r="F60" t="n">
+        <v>2903</v>
+      </c>
+      <c r="G60" t="s">
+        <v>16</v>
+      </c>
+      <c r="H60" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s">
+        <v>54</v>
+      </c>
+      <c r="B61" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C61" t="s">
+        <v>24</v>
+      </c>
+      <c r="D61" t="n">
+        <v>0.424651052756083</v>
+      </c>
+      <c r="E61" t="n">
+        <v>1795</v>
+      </c>
+      <c r="F61" t="n">
+        <v>4227</v>
+      </c>
+      <c r="G61" t="s">
+        <v>16</v>
+      </c>
+      <c r="H61" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s">
+        <v>54</v>
+      </c>
+      <c r="B62" s="1" t="n">
+        <v>45658</v>
+      </c>
+      <c r="C62" t="s">
+        <v>25</v>
+      </c>
+      <c r="D62" t="n">
+        <v>0.499999999999999</v>
+      </c>
+      <c r="E62" t="n">
+        <v>297</v>
+      </c>
+      <c r="F62" t="n">
+        <v>594</v>
+      </c>
+      <c r="G62" t="s">
+        <v>16</v>
+      </c>
+      <c r="H62" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s">
+        <v>54</v>
+      </c>
+      <c r="B63" s="1" t="n">
+        <v>45748</v>
+      </c>
+      <c r="C63" t="s">
+        <v>25</v>
+      </c>
+      <c r="D63" t="n">
+        <v>0.509389671361507</v>
+      </c>
+      <c r="E63" t="n">
+        <v>1302</v>
+      </c>
+      <c r="F63" t="n">
+        <v>2556</v>
+      </c>
+      <c r="G63" t="s">
+        <v>16</v>
+      </c>
+      <c r="H63" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s">
+        <v>54</v>
+      </c>
+      <c r="B64" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C64" t="s">
+        <v>25</v>
+      </c>
+      <c r="D64" t="n">
+        <v>0.520151567344144</v>
+      </c>
+      <c r="E64" t="n">
+        <v>1510</v>
+      </c>
+      <c r="F64" t="n">
+        <v>2903</v>
+      </c>
+      <c r="G64" t="s">
+        <v>16</v>
+      </c>
+      <c r="H64" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s">
+        <v>54</v>
+      </c>
+      <c r="B65" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C65" t="s">
+        <v>25</v>
+      </c>
+      <c r="D65" t="n">
+        <v>0.49609652235627</v>
+      </c>
+      <c r="E65" t="n">
+        <v>2097</v>
+      </c>
+      <c r="F65" t="n">
+        <v>4227</v>
+      </c>
+      <c r="G65" t="s">
+        <v>16</v>
+      </c>
+      <c r="H65" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s">
+        <v>54</v>
+      </c>
+      <c r="B66" s="1" t="n">
+        <v>45658</v>
+      </c>
+      <c r="C66" t="s">
+        <v>26</v>
+      </c>
+      <c r="D66" t="n">
+        <v>0.609427609427611</v>
+      </c>
+      <c r="E66" t="n">
+        <v>362</v>
+      </c>
+      <c r="F66" t="n">
+        <v>594</v>
+      </c>
+      <c r="G66" t="s">
+        <v>16</v>
+      </c>
+      <c r="H66" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s">
+        <v>54</v>
+      </c>
+      <c r="B67" s="1" t="n">
+        <v>45748</v>
+      </c>
+      <c r="C67" t="s">
+        <v>26</v>
+      </c>
+      <c r="D67" t="n">
+        <v>0.609546165884186</v>
+      </c>
+      <c r="E67" t="n">
+        <v>1558</v>
+      </c>
+      <c r="F67" t="n">
+        <v>2556</v>
+      </c>
+      <c r="G67" t="s">
+        <v>16</v>
+      </c>
+      <c r="H67" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s">
+        <v>54</v>
+      </c>
+      <c r="B68" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C68" t="s">
+        <v>26</v>
+      </c>
+      <c r="D68" t="n">
+        <v>0.635893902859119</v>
+      </c>
+      <c r="E68" t="n">
+        <v>1846</v>
+      </c>
+      <c r="F68" t="n">
+        <v>2903</v>
+      </c>
+      <c r="G68" t="s">
+        <v>16</v>
+      </c>
+      <c r="H68" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s">
+        <v>54</v>
+      </c>
+      <c r="B69" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C69" t="s">
+        <v>26</v>
+      </c>
+      <c r="D69" t="n">
+        <v>0.597350366690332</v>
+      </c>
+      <c r="E69" t="n">
+        <v>2525</v>
+      </c>
+      <c r="F69" t="n">
+        <v>4227</v>
+      </c>
+      <c r="G69" t="s">
+        <v>16</v>
+      </c>
+      <c r="H69" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s">
+        <v>54</v>
+      </c>
+      <c r="B70" s="1" t="n">
+        <v>45658</v>
+      </c>
+      <c r="C70" t="s">
+        <v>27</v>
+      </c>
+      <c r="D70" t="n">
+        <v>0.479797979797978</v>
+      </c>
+      <c r="E70" t="n">
+        <v>285</v>
+      </c>
+      <c r="F70" t="n">
+        <v>594</v>
+      </c>
+      <c r="G70" t="s">
+        <v>16</v>
+      </c>
+      <c r="H70" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s">
+        <v>54</v>
+      </c>
+      <c r="B71" s="1" t="n">
+        <v>45748</v>
+      </c>
+      <c r="C71" t="s">
+        <v>27</v>
+      </c>
+      <c r="D71" t="n">
+        <v>0.511737089201883</v>
+      </c>
+      <c r="E71" t="n">
+        <v>1308</v>
+      </c>
+      <c r="F71" t="n">
+        <v>2556</v>
+      </c>
+      <c r="G71" t="s">
+        <v>16</v>
+      </c>
+      <c r="H71" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s">
+        <v>54</v>
+      </c>
+      <c r="B72" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C72" t="s">
+        <v>27</v>
+      </c>
+      <c r="D72" t="n">
+        <v>0.538064071650033</v>
+      </c>
+      <c r="E72" t="n">
+        <v>1562</v>
+      </c>
+      <c r="F72" t="n">
+        <v>2903</v>
+      </c>
+      <c r="G72" t="s">
+        <v>16</v>
+      </c>
+      <c r="H72" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s">
+        <v>54</v>
+      </c>
+      <c r="B73" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C73" t="s">
+        <v>27</v>
+      </c>
+      <c r="D73" t="n">
+        <v>0.501064584811912</v>
+      </c>
+      <c r="E73" t="n">
+        <v>2118</v>
+      </c>
+      <c r="F73" t="n">
+        <v>4227</v>
+      </c>
+      <c r="G73" t="s">
+        <v>16</v>
+      </c>
+      <c r="H73" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s">
+        <v>54</v>
+      </c>
+      <c r="B74" s="1" t="n">
+        <v>45658</v>
+      </c>
+      <c r="C74" t="s">
+        <v>28</v>
+      </c>
+      <c r="D74" t="n">
+        <v>0.44107744107744</v>
+      </c>
+      <c r="E74" t="n">
+        <v>262</v>
+      </c>
+      <c r="F74" t="n">
+        <v>594</v>
+      </c>
+      <c r="G74" t="s">
+        <v>16</v>
+      </c>
+      <c r="H74" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s">
+        <v>54</v>
+      </c>
+      <c r="B75" s="1" t="n">
+        <v>45748</v>
+      </c>
+      <c r="C75" t="s">
+        <v>28</v>
+      </c>
+      <c r="D75" t="n">
+        <v>0.447574334898284</v>
+      </c>
+      <c r="E75" t="n">
+        <v>1144</v>
+      </c>
+      <c r="F75" t="n">
+        <v>2556</v>
+      </c>
+      <c r="G75" t="s">
+        <v>16</v>
+      </c>
+      <c r="H75" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s">
+        <v>54</v>
+      </c>
+      <c r="B76" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C76" t="s">
+        <v>28</v>
+      </c>
+      <c r="D76" t="n">
+        <v>0.450912848777142</v>
+      </c>
+      <c r="E76" t="n">
+        <v>1309</v>
+      </c>
+      <c r="F76" t="n">
+        <v>2903</v>
+      </c>
+      <c r="G76" t="s">
+        <v>16</v>
+      </c>
+      <c r="H76" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s">
+        <v>54</v>
+      </c>
+      <c r="B77" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C77" t="s">
+        <v>28</v>
+      </c>
+      <c r="D77" t="n">
+        <v>0.443340430565403</v>
+      </c>
+      <c r="E77" t="n">
+        <v>1874</v>
+      </c>
+      <c r="F77" t="n">
+        <v>4227</v>
+      </c>
+      <c r="G77" t="s">
+        <v>16</v>
+      </c>
+      <c r="H77" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s">
+        <v>54</v>
+      </c>
+      <c r="B78" s="1" t="n">
+        <v>45658</v>
+      </c>
+      <c r="C78" t="s">
+        <v>29</v>
+      </c>
+      <c r="D78" t="n">
+        <v>0.565656565656566</v>
+      </c>
+      <c r="E78" t="n">
+        <v>336</v>
+      </c>
+      <c r="F78" t="n">
+        <v>594</v>
+      </c>
+      <c r="G78" t="s">
+        <v>16</v>
+      </c>
+      <c r="H78" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="s">
+        <v>54</v>
+      </c>
+      <c r="B79" s="1" t="n">
+        <v>45748</v>
+      </c>
+      <c r="C79" t="s">
+        <v>29</v>
+      </c>
+      <c r="D79" t="n">
+        <v>0.570813771517994</v>
+      </c>
+      <c r="E79" t="n">
+        <v>1459</v>
+      </c>
+      <c r="F79" t="n">
+        <v>2556</v>
+      </c>
+      <c r="G79" t="s">
+        <v>16</v>
+      </c>
+      <c r="H79" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="s">
+        <v>54</v>
+      </c>
+      <c r="B80" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C80" t="s">
+        <v>29</v>
+      </c>
+      <c r="D80" t="n">
+        <v>0.585256631071318</v>
+      </c>
+      <c r="E80" t="n">
+        <v>1699</v>
+      </c>
+      <c r="F80" t="n">
+        <v>2903</v>
+      </c>
+      <c r="G80" t="s">
+        <v>16</v>
+      </c>
+      <c r="H80" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="s">
+        <v>54</v>
+      </c>
+      <c r="B81" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C81" t="s">
+        <v>29</v>
+      </c>
+      <c r="D81" t="n">
+        <v>0.573219777620065</v>
+      </c>
+      <c r="E81" t="n">
+        <v>2423</v>
+      </c>
+      <c r="F81" t="n">
+        <v>4227</v>
+      </c>
+      <c r="G81" t="s">
+        <v>16</v>
+      </c>
+      <c r="H81" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="s">
+        <v>54</v>
+      </c>
+      <c r="B82" s="1" t="n">
+        <v>45658</v>
+      </c>
+      <c r="C82" t="s">
+        <v>30</v>
+      </c>
+      <c r="D82" t="n">
+        <v>0.499999999999999</v>
+      </c>
+      <c r="E82" t="n">
+        <v>297</v>
+      </c>
+      <c r="F82" t="n">
+        <v>594</v>
+      </c>
+      <c r="G82" t="s">
+        <v>16</v>
+      </c>
+      <c r="H82" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="s">
+        <v>54</v>
+      </c>
+      <c r="B83" s="1" t="n">
+        <v>45748</v>
+      </c>
+      <c r="C83" t="s">
+        <v>30</v>
+      </c>
+      <c r="D83" t="n">
+        <v>0.495305164319255</v>
+      </c>
+      <c r="E83" t="n">
+        <v>1266</v>
+      </c>
+      <c r="F83" t="n">
+        <v>2556</v>
+      </c>
+      <c r="G83" t="s">
+        <v>16</v>
+      </c>
+      <c r="H83" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="s">
+        <v>54</v>
+      </c>
+      <c r="B84" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C84" t="s">
+        <v>30</v>
+      </c>
+      <c r="D84" t="n">
+        <v>0.500172235618345</v>
+      </c>
+      <c r="E84" t="n">
+        <v>1452</v>
+      </c>
+      <c r="F84" t="n">
+        <v>2903</v>
+      </c>
+      <c r="G84" t="s">
+        <v>16</v>
+      </c>
+      <c r="H84" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="s">
+        <v>54</v>
+      </c>
+      <c r="B85" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C85" t="s">
+        <v>30</v>
+      </c>
+      <c r="D85" t="n">
+        <v>0.488052992666183</v>
+      </c>
+      <c r="E85" t="n">
+        <v>2063</v>
+      </c>
+      <c r="F85" t="n">
+        <v>4227</v>
+      </c>
+      <c r="G85" t="s">
+        <v>16</v>
+      </c>
+      <c r="H85" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="s">
+        <v>54</v>
+      </c>
+      <c r="B86" s="1" t="n">
+        <v>45658</v>
+      </c>
+      <c r="C86" t="s">
+        <v>31</v>
+      </c>
+      <c r="D86" t="n">
+        <v>0.547138047138047</v>
+      </c>
+      <c r="E86" t="n">
+        <v>325</v>
+      </c>
+      <c r="F86" t="n">
+        <v>594</v>
+      </c>
+      <c r="G86" t="s">
+        <v>32</v>
+      </c>
+      <c r="H86" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="s">
+        <v>54</v>
+      </c>
+      <c r="B87" s="1" t="n">
+        <v>45748</v>
+      </c>
+      <c r="C87" t="s">
+        <v>31</v>
+      </c>
+      <c r="D87" t="n">
+        <v>0.549295774647887</v>
+      </c>
+      <c r="E87" t="n">
+        <v>1404</v>
+      </c>
+      <c r="F87" t="n">
+        <v>2556</v>
+      </c>
+      <c r="G87" t="s">
+        <v>32</v>
+      </c>
+      <c r="H87" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="s">
+        <v>54</v>
+      </c>
+      <c r="B88" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C88" t="s">
+        <v>31</v>
+      </c>
+      <c r="D88" t="n">
+        <v>0.57354460902516</v>
+      </c>
+      <c r="E88" t="n">
+        <v>1665</v>
+      </c>
+      <c r="F88" t="n">
+        <v>2903</v>
+      </c>
+      <c r="G88" t="s">
+        <v>32</v>
+      </c>
+      <c r="H88" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="s">
+        <v>54</v>
+      </c>
+      <c r="B89" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C89" t="s">
+        <v>31</v>
+      </c>
+      <c r="D89" t="n">
+        <v>0.537733617222613</v>
+      </c>
+      <c r="E89" t="n">
+        <v>2273</v>
+      </c>
+      <c r="F89" t="n">
+        <v>4227</v>
+      </c>
+      <c r="G89" t="s">
+        <v>32</v>
+      </c>
+      <c r="H89" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="s">
+        <v>54</v>
+      </c>
+      <c r="B90" s="1" t="n">
+        <v>45658</v>
+      </c>
+      <c r="C90" t="s">
+        <v>33</v>
+      </c>
+      <c r="D90" t="n">
+        <v>0.513468013468012</v>
+      </c>
+      <c r="E90" t="n">
+        <v>305</v>
+      </c>
+      <c r="F90" t="n">
+        <v>594</v>
+      </c>
+      <c r="G90" t="s">
+        <v>32</v>
+      </c>
+      <c r="H90" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="s">
+        <v>54</v>
+      </c>
+      <c r="B91" s="1" t="n">
+        <v>45748</v>
+      </c>
+      <c r="C91" t="s">
+        <v>33</v>
+      </c>
+      <c r="D91" t="n">
+        <v>0.525039123630676</v>
+      </c>
+      <c r="E91" t="n">
+        <v>1342</v>
+      </c>
+      <c r="F91" t="n">
+        <v>2556</v>
+      </c>
+      <c r="G91" t="s">
+        <v>32</v>
+      </c>
+      <c r="H91" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="s">
+        <v>54</v>
+      </c>
+      <c r="B92" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C92" t="s">
+        <v>33</v>
+      </c>
+      <c r="D92" t="n">
+        <v>0.540130899069943</v>
+      </c>
+      <c r="E92" t="n">
+        <v>1568</v>
+      </c>
+      <c r="F92" t="n">
+        <v>2903</v>
+      </c>
+      <c r="G92" t="s">
+        <v>32</v>
+      </c>
+      <c r="H92" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="s">
+        <v>54</v>
+      </c>
+      <c r="B93" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C93" t="s">
+        <v>33</v>
+      </c>
+      <c r="D93" t="n">
+        <v>0.506978944878154</v>
+      </c>
+      <c r="E93" t="n">
+        <v>2143</v>
+      </c>
+      <c r="F93" t="n">
+        <v>4227</v>
+      </c>
+      <c r="G93" t="s">
+        <v>32</v>
+      </c>
+      <c r="H93" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="s">
+        <v>54</v>
+      </c>
+      <c r="B94" s="1" t="n">
+        <v>45658</v>
+      </c>
+      <c r="C94" t="s">
+        <v>34</v>
+      </c>
+      <c r="D94" t="n">
+        <v>0.590909090909092</v>
+      </c>
+      <c r="E94" t="n">
+        <v>351</v>
+      </c>
+      <c r="F94" t="n">
+        <v>594</v>
+      </c>
+      <c r="G94" t="s">
+        <v>32</v>
+      </c>
+      <c r="H94" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="s">
+        <v>54</v>
+      </c>
+      <c r="B95" s="1" t="n">
+        <v>45748</v>
+      </c>
+      <c r="C95" t="s">
+        <v>34</v>
+      </c>
+      <c r="D95" t="n">
+        <v>0.573943661971828</v>
+      </c>
+      <c r="E95" t="n">
+        <v>1467</v>
+      </c>
+      <c r="F95" t="n">
+        <v>2556</v>
+      </c>
+      <c r="G95" t="s">
+        <v>32</v>
+      </c>
+      <c r="H95" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="s">
+        <v>54</v>
+      </c>
+      <c r="B96" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C96" t="s">
+        <v>34</v>
+      </c>
+      <c r="D96" t="n">
+        <v>0.614192214950061</v>
+      </c>
+      <c r="E96" t="n">
+        <v>1783</v>
+      </c>
+      <c r="F96" t="n">
+        <v>2903</v>
+      </c>
+      <c r="G96" t="s">
+        <v>32</v>
+      </c>
+      <c r="H96" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="s">
+        <v>54</v>
+      </c>
+      <c r="B97" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C97" t="s">
+        <v>34</v>
+      </c>
+      <c r="D97" t="n">
+        <v>0.600425833924778</v>
+      </c>
+      <c r="E97" t="n">
+        <v>2538</v>
+      </c>
+      <c r="F97" t="n">
+        <v>4227</v>
+      </c>
+      <c r="G97" t="s">
+        <v>32</v>
+      </c>
+      <c r="H97" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="s">
+        <v>54</v>
+      </c>
+      <c r="B98" s="1" t="n">
+        <v>45658</v>
+      </c>
+      <c r="C98" t="s">
+        <v>35</v>
+      </c>
+      <c r="D98" t="n">
+        <v>0.558922558922559</v>
+      </c>
+      <c r="E98" t="n">
+        <v>332</v>
+      </c>
+      <c r="F98" t="n">
+        <v>594</v>
+      </c>
+      <c r="G98" t="s">
+        <v>32</v>
+      </c>
+      <c r="H98" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="s">
+        <v>54</v>
+      </c>
+      <c r="B99" s="1" t="n">
+        <v>45748</v>
+      </c>
+      <c r="C99" t="s">
+        <v>35</v>
+      </c>
+      <c r="D99" t="n">
+        <v>0.575117370892015</v>
+      </c>
+      <c r="E99" t="n">
+        <v>1470</v>
+      </c>
+      <c r="F99" t="n">
+        <v>2556</v>
+      </c>
+      <c r="G99" t="s">
+        <v>32</v>
+      </c>
+      <c r="H99" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="s">
+        <v>54</v>
+      </c>
+      <c r="B100" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C100" t="s">
+        <v>35</v>
+      </c>
+      <c r="D100" t="n">
+        <v>0.59972442301069</v>
+      </c>
+      <c r="E100" t="n">
+        <v>1741</v>
+      </c>
+      <c r="F100" t="n">
+        <v>2903</v>
+      </c>
+      <c r="G100" t="s">
+        <v>32</v>
+      </c>
+      <c r="H100" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="s">
+        <v>54</v>
+      </c>
+      <c r="B101" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C101" t="s">
+        <v>35</v>
+      </c>
+      <c r="D101" t="n">
+        <v>0.572746628814765</v>
+      </c>
+      <c r="E101" t="n">
+        <v>2421</v>
+      </c>
+      <c r="F101" t="n">
+        <v>4227</v>
+      </c>
+      <c r="G101" t="s">
+        <v>32</v>
+      </c>
+      <c r="H101" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="s">
+        <v>54</v>
+      </c>
+      <c r="B102" s="1" t="n">
+        <v>45658</v>
+      </c>
+      <c r="C102" t="s">
+        <v>36</v>
+      </c>
+      <c r="D102" t="n">
+        <v>0.48148148148148</v>
+      </c>
+      <c r="E102" t="n">
+        <v>286</v>
+      </c>
+      <c r="F102" t="n">
+        <v>594</v>
+      </c>
+      <c r="G102" t="s">
+        <v>32</v>
+      </c>
+      <c r="H102" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="s">
+        <v>54</v>
+      </c>
+      <c r="B103" s="1" t="n">
+        <v>45748</v>
+      </c>
+      <c r="C103" t="s">
+        <v>36</v>
+      </c>
+      <c r="D103" t="n">
+        <v>0.493740219092338</v>
+      </c>
+      <c r="E103" t="n">
+        <v>1262</v>
+      </c>
+      <c r="F103" t="n">
+        <v>2556</v>
+      </c>
+      <c r="G103" t="s">
+        <v>32</v>
+      </c>
+      <c r="H103" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="s">
+        <v>54</v>
+      </c>
+      <c r="B104" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C104" t="s">
+        <v>36</v>
+      </c>
+      <c r="D104" t="n">
+        <v>0.496383052015176</v>
+      </c>
+      <c r="E104" t="n">
+        <v>1441</v>
+      </c>
+      <c r="F104" t="n">
+        <v>2903</v>
+      </c>
+      <c r="G104" t="s">
+        <v>32</v>
+      </c>
+      <c r="H104" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="s">
+        <v>54</v>
+      </c>
+      <c r="B105" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C105" t="s">
+        <v>36</v>
+      </c>
+      <c r="D105" t="n">
+        <v>0.473621954104555</v>
+      </c>
+      <c r="E105" t="n">
+        <v>2002</v>
+      </c>
+      <c r="F105" t="n">
+        <v>4227</v>
+      </c>
+      <c r="G105" t="s">
+        <v>32</v>
+      </c>
+      <c r="H105" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="s">
+        <v>54</v>
+      </c>
+      <c r="B106" s="1" t="n">
+        <v>45658</v>
+      </c>
+      <c r="C106" t="s">
+        <v>37</v>
+      </c>
+      <c r="D106" t="n">
+        <v>0.520202020202019</v>
+      </c>
+      <c r="E106" t="n">
+        <v>309</v>
+      </c>
+      <c r="F106" t="n">
+        <v>594</v>
+      </c>
+      <c r="G106" t="s">
+        <v>32</v>
+      </c>
+      <c r="H106" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="s">
+        <v>54</v>
+      </c>
+      <c r="B107" s="1" t="n">
+        <v>45748</v>
+      </c>
+      <c r="C107" t="s">
+        <v>37</v>
+      </c>
+      <c r="D107" t="n">
+        <v>0.539123630672928</v>
+      </c>
+      <c r="E107" t="n">
+        <v>1378</v>
+      </c>
+      <c r="F107" t="n">
+        <v>2556</v>
+      </c>
+      <c r="G107" t="s">
+        <v>32</v>
+      </c>
+      <c r="H107" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="s">
+        <v>54</v>
+      </c>
+      <c r="B108" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C108" t="s">
+        <v>37</v>
+      </c>
+      <c r="D108" t="n">
+        <v>0.550465036169495</v>
+      </c>
+      <c r="E108" t="n">
+        <v>1598</v>
+      </c>
+      <c r="F108" t="n">
+        <v>2903</v>
+      </c>
+      <c r="G108" t="s">
+        <v>32</v>
+      </c>
+      <c r="H108" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="s">
+        <v>54</v>
+      </c>
+      <c r="B109" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C109" t="s">
+        <v>37</v>
+      </c>
+      <c r="D109" t="n">
+        <v>0.541991956470307</v>
+      </c>
+      <c r="E109" t="n">
+        <v>2291</v>
+      </c>
+      <c r="F109" t="n">
+        <v>4227</v>
+      </c>
+      <c r="G109" t="s">
+        <v>32</v>
+      </c>
+      <c r="H109" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="s">
+        <v>54</v>
+      </c>
+      <c r="B110" s="1" t="n">
+        <v>45658</v>
+      </c>
+      <c r="C110" t="s">
+        <v>38</v>
+      </c>
+      <c r="D110" t="n">
+        <v>0.542087542087542</v>
+      </c>
+      <c r="E110" t="n">
+        <v>322</v>
+      </c>
+      <c r="F110" t="n">
+        <v>594</v>
+      </c>
+      <c r="G110" t="s">
+        <v>32</v>
+      </c>
+      <c r="H110" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="s">
+        <v>54</v>
+      </c>
+      <c r="B111" s="1" t="n">
+        <v>45748</v>
+      </c>
+      <c r="C111" t="s">
+        <v>38</v>
+      </c>
+      <c r="D111" t="n">
+        <v>0.520344287949925</v>
+      </c>
+      <c r="E111" t="n">
+        <v>1330</v>
+      </c>
+      <c r="F111" t="n">
+        <v>2556</v>
+      </c>
+      <c r="G111" t="s">
+        <v>32</v>
+      </c>
+      <c r="H111" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="s">
+        <v>54</v>
+      </c>
+      <c r="B112" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C112" t="s">
+        <v>38</v>
+      </c>
+      <c r="D112" t="n">
+        <v>0.555287633482619</v>
+      </c>
+      <c r="E112" t="n">
+        <v>1612</v>
+      </c>
+      <c r="F112" t="n">
+        <v>2903</v>
+      </c>
+      <c r="G112" t="s">
+        <v>32</v>
+      </c>
+      <c r="H112" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="s">
+        <v>54</v>
+      </c>
+      <c r="B113" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C113" t="s">
+        <v>38</v>
+      </c>
+      <c r="D113" t="n">
+        <v>0.524485450674231</v>
+      </c>
+      <c r="E113" t="n">
+        <v>2217</v>
+      </c>
+      <c r="F113" t="n">
+        <v>4227</v>
+      </c>
+      <c r="G113" t="s">
+        <v>32</v>
+      </c>
+      <c r="H113" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="s">
+        <v>54</v>
+      </c>
+      <c r="B114" s="1" t="n">
+        <v>45658</v>
+      </c>
+      <c r="C114" t="s">
+        <v>39</v>
+      </c>
+      <c r="D114" t="n">
+        <v>0.377104377104376</v>
+      </c>
+      <c r="E114" t="n">
+        <v>224</v>
+      </c>
+      <c r="F114" t="n">
+        <v>594</v>
+      </c>
+      <c r="G114" t="s">
+        <v>32</v>
+      </c>
+      <c r="H114" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="s">
+        <v>54</v>
+      </c>
+      <c r="B115" s="1" t="n">
+        <v>45748</v>
+      </c>
+      <c r="C115" t="s">
+        <v>39</v>
+      </c>
+      <c r="D115" t="n">
+        <v>0.377934272300474</v>
+      </c>
+      <c r="E115" t="n">
+        <v>966</v>
+      </c>
+      <c r="F115" t="n">
+        <v>2556</v>
+      </c>
+      <c r="G115" t="s">
+        <v>32</v>
+      </c>
+      <c r="H115" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="s">
+        <v>54</v>
+      </c>
+      <c r="B116" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C116" t="s">
+        <v>39</v>
+      </c>
+      <c r="D116" t="n">
+        <v>0.405098174302457</v>
+      </c>
+      <c r="E116" t="n">
+        <v>1176</v>
+      </c>
+      <c r="F116" t="n">
+        <v>2903</v>
+      </c>
+      <c r="G116" t="s">
+        <v>32</v>
+      </c>
+      <c r="H116" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="s">
+        <v>54</v>
+      </c>
+      <c r="B117" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C117" t="s">
+        <v>39</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.361249112845983</v>
+      </c>
+      <c r="E117" t="n">
+        <v>1527</v>
+      </c>
+      <c r="F117" t="n">
+        <v>4227</v>
+      </c>
+      <c r="G117" t="s">
+        <v>32</v>
+      </c>
+      <c r="H117" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="s">
+        <v>54</v>
+      </c>
+      <c r="B118" s="1" t="n">
+        <v>45658</v>
+      </c>
+      <c r="C118" t="s">
+        <v>40</v>
+      </c>
+      <c r="D118" t="n">
+        <v>0.595959595959597</v>
+      </c>
+      <c r="E118" t="n">
+        <v>354</v>
+      </c>
+      <c r="F118" t="n">
+        <v>594</v>
+      </c>
+      <c r="G118" t="s">
+        <v>32</v>
+      </c>
+      <c r="H118" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="s">
+        <v>54</v>
+      </c>
+      <c r="B119" s="1" t="n">
+        <v>45748</v>
+      </c>
+      <c r="C119" t="s">
+        <v>40</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.595461658841934</v>
+      </c>
+      <c r="E119" t="n">
+        <v>1522</v>
+      </c>
+      <c r="F119" t="n">
+        <v>2556</v>
+      </c>
+      <c r="G119" t="s">
+        <v>32</v>
+      </c>
+      <c r="H119" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="s">
+        <v>54</v>
+      </c>
+      <c r="B120" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C120" t="s">
+        <v>40</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.604891491560465</v>
+      </c>
+      <c r="E120" t="n">
+        <v>1756</v>
+      </c>
+      <c r="F120" t="n">
+        <v>2903</v>
+      </c>
+      <c r="G120" t="s">
+        <v>32</v>
+      </c>
+      <c r="H120" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="s">
+        <v>54</v>
+      </c>
+      <c r="B121" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C121" t="s">
+        <v>40</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.611544830849313</v>
+      </c>
+      <c r="E121" t="n">
+        <v>2585</v>
+      </c>
+      <c r="F121" t="n">
+        <v>4227</v>
+      </c>
+      <c r="G121" t="s">
+        <v>32</v>
+      </c>
+      <c r="H121" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="s">
+        <v>54</v>
+      </c>
+      <c r="B122" s="1" t="n">
+        <v>45658</v>
+      </c>
+      <c r="C122" t="s">
+        <v>41</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.53030303030303</v>
+      </c>
+      <c r="E122" t="n">
+        <v>315</v>
+      </c>
+      <c r="F122" t="n">
+        <v>594</v>
+      </c>
+      <c r="G122" t="s">
+        <v>32</v>
+      </c>
+      <c r="H122" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="s">
+        <v>54</v>
+      </c>
+      <c r="B123" s="1" t="n">
+        <v>45748</v>
+      </c>
+      <c r="C123" t="s">
+        <v>41</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.510172143974966</v>
+      </c>
+      <c r="E123" t="n">
+        <v>1304</v>
+      </c>
+      <c r="F123" t="n">
+        <v>2556</v>
+      </c>
+      <c r="G123" t="s">
+        <v>32</v>
+      </c>
+      <c r="H123" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="s">
+        <v>54</v>
+      </c>
+      <c r="B124" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C124" t="s">
+        <v>41</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.520151567344144</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1510</v>
+      </c>
+      <c r="F124" t="n">
+        <v>2903</v>
+      </c>
+      <c r="G124" t="s">
+        <v>32</v>
+      </c>
+      <c r="H124" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="s">
+        <v>54</v>
+      </c>
+      <c r="B125" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C125" t="s">
+        <v>41</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.484977525431737</v>
+      </c>
+      <c r="E125" t="n">
+        <v>2050</v>
+      </c>
+      <c r="F125" t="n">
+        <v>4227</v>
+      </c>
+      <c r="G125" t="s">
+        <v>32</v>
+      </c>
+      <c r="H125" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="s">
+        <v>54</v>
+      </c>
+      <c r="B126" s="1" t="n">
+        <v>45658</v>
+      </c>
+      <c r="C126" t="s">
+        <v>42</v>
+      </c>
+      <c r="D126" t="n">
+        <v>0.569023569023569</v>
+      </c>
+      <c r="E126" t="n">
+        <v>338</v>
+      </c>
+      <c r="F126" t="n">
+        <v>594</v>
+      </c>
+      <c r="G126" t="s">
+        <v>32</v>
+      </c>
+      <c r="H126" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="s">
+        <v>54</v>
+      </c>
+      <c r="B127" s="1" t="n">
+        <v>45748</v>
+      </c>
+      <c r="C127" t="s">
+        <v>42</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.582159624413141</v>
+      </c>
+      <c r="E127" t="n">
+        <v>1488</v>
+      </c>
+      <c r="F127" t="n">
+        <v>2556</v>
+      </c>
+      <c r="G127" t="s">
+        <v>32</v>
+      </c>
+      <c r="H127" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="s">
+        <v>54</v>
+      </c>
+      <c r="B128" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C128" t="s">
+        <v>42</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.608680675163634</v>
+      </c>
+      <c r="E128" t="n">
+        <v>1767</v>
+      </c>
+      <c r="F128" t="n">
+        <v>2903</v>
+      </c>
+      <c r="G128" t="s">
+        <v>32</v>
+      </c>
+      <c r="H128" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="s">
+        <v>54</v>
+      </c>
+      <c r="B129" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C129" t="s">
+        <v>42</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.574166075230664</v>
+      </c>
+      <c r="E129" t="n">
+        <v>2427</v>
+      </c>
+      <c r="F129" t="n">
+        <v>4227</v>
+      </c>
+      <c r="G129" t="s">
+        <v>32</v>
+      </c>
+      <c r="H129" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="s">
+        <v>54</v>
+      </c>
+      <c r="B130" s="1" t="n">
+        <v>45658</v>
+      </c>
+      <c r="C130" t="s">
+        <v>43</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.612794612794614</v>
+      </c>
+      <c r="E130" t="n">
+        <v>364</v>
+      </c>
+      <c r="F130" t="n">
+        <v>594</v>
+      </c>
+      <c r="G130" t="s">
+        <v>32</v>
+      </c>
+      <c r="H130" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="s">
+        <v>54</v>
+      </c>
+      <c r="B131" s="1" t="n">
+        <v>45748</v>
+      </c>
+      <c r="C131" t="s">
+        <v>43</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.6177621283255</v>
+      </c>
+      <c r="E131" t="n">
+        <v>1579</v>
+      </c>
+      <c r="F131" t="n">
+        <v>2556</v>
+      </c>
+      <c r="G131" t="s">
+        <v>32</v>
+      </c>
+      <c r="H131" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="s">
+        <v>54</v>
+      </c>
+      <c r="B132" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C132" t="s">
+        <v>43</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.623492938339658</v>
+      </c>
+      <c r="E132" t="n">
+        <v>1810</v>
+      </c>
+      <c r="F132" t="n">
+        <v>2903</v>
+      </c>
+      <c r="G132" t="s">
+        <v>32</v>
+      </c>
+      <c r="H132" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="s">
+        <v>54</v>
+      </c>
+      <c r="B133" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C133" t="s">
+        <v>43</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.614620298083759</v>
+      </c>
+      <c r="E133" t="n">
+        <v>2598</v>
+      </c>
+      <c r="F133" t="n">
+        <v>4227</v>
+      </c>
+      <c r="G133" t="s">
+        <v>32</v>
+      </c>
+      <c r="H133" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="s">
+        <v>54</v>
+      </c>
+      <c r="B134" s="1" t="n">
+        <v>45658</v>
+      </c>
+      <c r="C134" t="s">
+        <v>44</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.552188552188552</v>
+      </c>
+      <c r="E134" t="n">
+        <v>328</v>
+      </c>
+      <c r="F134" t="n">
+        <v>594</v>
+      </c>
+      <c r="G134" t="s">
+        <v>32</v>
+      </c>
+      <c r="H134" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="s">
+        <v>54</v>
+      </c>
+      <c r="B135" s="1" t="n">
+        <v>45748</v>
+      </c>
+      <c r="C135" t="s">
+        <v>44</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.588028169014079</v>
+      </c>
+      <c r="E135" t="n">
+        <v>1503</v>
+      </c>
+      <c r="F135" t="n">
+        <v>2556</v>
+      </c>
+      <c r="G135" t="s">
+        <v>32</v>
+      </c>
+      <c r="H135" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="s">
+        <v>54</v>
+      </c>
+      <c r="B136" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C136" t="s">
+        <v>44</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.592146055804352</v>
+      </c>
+      <c r="E136" t="n">
+        <v>1719</v>
+      </c>
+      <c r="F136" t="n">
+        <v>2903</v>
+      </c>
+      <c r="G136" t="s">
+        <v>32</v>
+      </c>
+      <c r="H136" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="s">
+        <v>54</v>
+      </c>
+      <c r="B137" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C137" t="s">
+        <v>44</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.568251715164422</v>
+      </c>
+      <c r="E137" t="n">
+        <v>2402</v>
+      </c>
+      <c r="F137" t="n">
+        <v>4227</v>
+      </c>
+      <c r="G137" t="s">
+        <v>32</v>
+      </c>
+      <c r="H137" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="s">
+        <v>54</v>
+      </c>
+      <c r="B138" s="1" t="n">
+        <v>45658</v>
+      </c>
+      <c r="C138" t="s">
+        <v>45</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.621212121212123</v>
+      </c>
+      <c r="E138" t="n">
+        <v>369</v>
+      </c>
+      <c r="F138" t="n">
+        <v>594</v>
+      </c>
+      <c r="G138" t="s">
+        <v>32</v>
+      </c>
+      <c r="H138" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="s">
+        <v>54</v>
+      </c>
+      <c r="B139" s="1" t="n">
+        <v>45748</v>
+      </c>
+      <c r="C139" t="s">
+        <v>45</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.626369327073542</v>
+      </c>
+      <c r="E139" t="n">
+        <v>1601</v>
+      </c>
+      <c r="F139" t="n">
+        <v>2556</v>
+      </c>
+      <c r="G139" t="s">
+        <v>32</v>
+      </c>
+      <c r="H139" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="s">
+        <v>54</v>
+      </c>
+      <c r="B140" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C140" t="s">
+        <v>45</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.657940062004829</v>
+      </c>
+      <c r="E140" t="n">
+        <v>1910</v>
+      </c>
+      <c r="F140" t="n">
+        <v>2903</v>
+      </c>
+      <c r="G140" t="s">
+        <v>32</v>
+      </c>
+      <c r="H140" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="s">
+        <v>54</v>
+      </c>
+      <c r="B141" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C141" t="s">
+        <v>45</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.643955524012319</v>
+      </c>
+      <c r="E141" t="n">
+        <v>2722</v>
+      </c>
+      <c r="F141" t="n">
+        <v>4227</v>
+      </c>
+      <c r="G141" t="s">
+        <v>32</v>
+      </c>
+      <c r="H141" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="s">
+        <v>54</v>
+      </c>
+      <c r="B142" s="1" t="n">
+        <v>45658</v>
+      </c>
+      <c r="C142" t="s">
+        <v>46</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.415824915824915</v>
+      </c>
+      <c r="E142" t="n">
+        <v>247</v>
+      </c>
+      <c r="F142" t="n">
+        <v>594</v>
+      </c>
+      <c r="G142" t="s">
+        <v>32</v>
+      </c>
+      <c r="H142" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="s">
+        <v>54</v>
+      </c>
+      <c r="B143" s="1" t="n">
+        <v>45748</v>
+      </c>
+      <c r="C143" t="s">
+        <v>46</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.421752738654152</v>
+      </c>
+      <c r="E143" t="n">
+        <v>1078</v>
+      </c>
+      <c r="F143" t="n">
+        <v>2556</v>
+      </c>
+      <c r="G143" t="s">
+        <v>32</v>
+      </c>
+      <c r="H143" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="s">
+        <v>54</v>
+      </c>
+      <c r="B144" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C144" t="s">
+        <v>46</v>
+      </c>
+      <c r="D144" t="n">
+        <v>0.451946262487098</v>
+      </c>
+      <c r="E144" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F144" t="n">
+        <v>2903</v>
+      </c>
+      <c r="G144" t="s">
+        <v>32</v>
+      </c>
+      <c r="H144" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="s">
+        <v>54</v>
+      </c>
+      <c r="B145" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C145" t="s">
+        <v>46</v>
+      </c>
+      <c r="D145" t="n">
+        <v>0.425833924769331</v>
+      </c>
+      <c r="E145" t="n">
+        <v>1800</v>
+      </c>
+      <c r="F145" t="n">
+        <v>4227</v>
+      </c>
+      <c r="G145" t="s">
+        <v>32</v>
+      </c>
+      <c r="H145" t="s">
+        <v>9</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B2" s="1" t="n">
+        <v>45658</v>
+      </c>
+      <c r="C2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.410958904109589</v>
+      </c>
+      <c r="E2" t="n">
+        <v>30</v>
+      </c>
+      <c r="F2" t="n">
+        <v>73</v>
+      </c>
+      <c r="G2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B3" s="1" t="n">
+        <v>45748</v>
+      </c>
+      <c r="C3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.432515337423312</v>
+      </c>
+      <c r="E3" t="n">
+        <v>141</v>
+      </c>
+      <c r="F3" t="n">
+        <v>326</v>
+      </c>
+      <c r="G3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B4" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.495073891625615</v>
+      </c>
+      <c r="E4" t="n">
+        <v>201</v>
+      </c>
+      <c r="F4" t="n">
+        <v>406</v>
+      </c>
+      <c r="G4" t="s">
+        <v>8</v>
+      </c>
+      <c r="H4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>55</v>
+      </c>
+      <c r="B5" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.469740634005767</v>
+      </c>
+      <c r="E5" t="n">
+        <v>326</v>
+      </c>
+      <c r="F5" t="n">
+        <v>694</v>
+      </c>
+      <c r="G5" t="s">
+        <v>8</v>
+      </c>
+      <c r="H5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>55</v>
+      </c>
+      <c r="B6" s="1" t="n">
+        <v>45658</v>
+      </c>
+      <c r="C6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.808219178082193</v>
+      </c>
+      <c r="E6" t="n">
+        <v>59</v>
+      </c>
+      <c r="F6" t="n">
+        <v>73</v>
+      </c>
+      <c r="G6" t="s">
+        <v>8</v>
+      </c>
+      <c r="H6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>55</v>
+      </c>
+      <c r="B7" s="1" t="n">
+        <v>45748</v>
+      </c>
+      <c r="C7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.901840490797543</v>
+      </c>
+      <c r="E7" t="n">
+        <v>294</v>
+      </c>
+      <c r="F7" t="n">
+        <v>326</v>
+      </c>
+      <c r="G7" t="s">
+        <v>8</v>
+      </c>
+      <c r="H7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>55</v>
+      </c>
+      <c r="B8" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.911330049261092</v>
+      </c>
+      <c r="E8" t="n">
+        <v>370</v>
+      </c>
+      <c r="F8" t="n">
+        <v>406</v>
+      </c>
+      <c r="G8" t="s">
+        <v>8</v>
+      </c>
+      <c r="H8" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>55</v>
+      </c>
+      <c r="B9" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C9" t="s">
+        <v>10</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.909221902017302</v>
+      </c>
+      <c r="E9" t="n">
+        <v>631</v>
+      </c>
+      <c r="F9" t="n">
+        <v>694</v>
+      </c>
+      <c r="G9" t="s">
+        <v>8</v>
+      </c>
+      <c r="H9" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>55</v>
+      </c>
+      <c r="B10" s="1" t="n">
+        <v>45658</v>
+      </c>
+      <c r="C10" t="s">
+        <v>11</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.406779661016949</v>
+      </c>
+      <c r="E10" t="n">
+        <v>24</v>
+      </c>
+      <c r="F10" t="n">
+        <v>59</v>
+      </c>
+      <c r="G10" t="s">
+        <v>8</v>
+      </c>
+      <c r="H10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>55</v>
+      </c>
+      <c r="B11" s="1" t="n">
+        <v>45748</v>
+      </c>
+      <c r="C11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E11" t="n">
+        <v>147</v>
+      </c>
+      <c r="F11" t="n">
+        <v>294</v>
+      </c>
+      <c r="G11" t="s">
+        <v>8</v>
+      </c>
+      <c r="H11" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>55</v>
+      </c>
+      <c r="B12" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C12" t="s">
+        <v>11</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.57297297297297</v>
+      </c>
+      <c r="E12" t="n">
+        <v>212</v>
+      </c>
+      <c r="F12" t="n">
+        <v>370</v>
+      </c>
+      <c r="G12" t="s">
+        <v>8</v>
+      </c>
+      <c r="H12" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>55</v>
+      </c>
+      <c r="B13" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C13" t="s">
+        <v>11</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.603803486529318</v>
+      </c>
+      <c r="E13" t="n">
+        <v>381</v>
+      </c>
+      <c r="F13" t="n">
+        <v>631</v>
+      </c>
+      <c r="G13" t="s">
+        <v>8</v>
+      </c>
+      <c r="H13" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>55</v>
+      </c>
+      <c r="B14" s="1" t="n">
+        <v>45658</v>
+      </c>
+      <c r="C14" t="s">
+        <v>12</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.542372881355932</v>
+      </c>
+      <c r="E14" t="n">
+        <v>32</v>
+      </c>
+      <c r="F14" t="n">
+        <v>59</v>
+      </c>
+      <c r="G14" t="s">
+        <v>8</v>
+      </c>
+      <c r="H14" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>55</v>
+      </c>
+      <c r="B15" s="1" t="n">
+        <v>45748</v>
+      </c>
+      <c r="C15" t="s">
+        <v>12</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.61904761904762</v>
+      </c>
+      <c r="E15" t="n">
+        <v>182</v>
+      </c>
+      <c r="F15" t="n">
+        <v>294</v>
+      </c>
+      <c r="G15" t="s">
+        <v>8</v>
+      </c>
+      <c r="H15" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>55</v>
+      </c>
+      <c r="B16" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C16" t="s">
+        <v>12</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.608108108108104</v>
+      </c>
+      <c r="E16" t="n">
+        <v>225</v>
+      </c>
+      <c r="F16" t="n">
+        <v>370</v>
+      </c>
+      <c r="G16" t="s">
+        <v>8</v>
+      </c>
+      <c r="H16" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>55</v>
+      </c>
+      <c r="B17" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C17" t="s">
+        <v>12</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.602218700475435</v>
+      </c>
+      <c r="E17" t="n">
+        <v>380</v>
+      </c>
+      <c r="F17" t="n">
+        <v>631</v>
+      </c>
+      <c r="G17" t="s">
+        <v>8</v>
+      </c>
+      <c r="H17" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>55</v>
+      </c>
+      <c r="B18" s="1" t="n">
+        <v>45658</v>
+      </c>
+      <c r="C18" t="s">
+        <v>13</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.372881355932204</v>
+      </c>
+      <c r="E18" t="n">
+        <v>22</v>
+      </c>
+      <c r="F18" t="n">
+        <v>59</v>
+      </c>
+      <c r="G18" t="s">
+        <v>8</v>
+      </c>
+      <c r="H18" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>55</v>
+      </c>
+      <c r="B19" s="1" t="n">
+        <v>45748</v>
+      </c>
+      <c r="C19" t="s">
+        <v>13</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.45578231292517</v>
+      </c>
+      <c r="E19" t="n">
+        <v>134</v>
+      </c>
+      <c r="F19" t="n">
+        <v>294</v>
+      </c>
+      <c r="G19" t="s">
+        <v>8</v>
+      </c>
+      <c r="H19" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>55</v>
+      </c>
+      <c r="B20" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C20" t="s">
+        <v>13</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.483783783783781</v>
+      </c>
+      <c r="E20" t="n">
+        <v>179</v>
+      </c>
+      <c r="F20" t="n">
+        <v>370</v>
+      </c>
+      <c r="G20" t="s">
+        <v>8</v>
+      </c>
+      <c r="H20" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>55</v>
+      </c>
+      <c r="B21" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C21" t="s">
+        <v>13</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.489698890649764</v>
+      </c>
+      <c r="E21" t="n">
+        <v>309</v>
+      </c>
+      <c r="F21" t="n">
+        <v>631</v>
+      </c>
+      <c r="G21" t="s">
+        <v>8</v>
+      </c>
+      <c r="H21" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>55</v>
+      </c>
+      <c r="B22" s="1" t="n">
+        <v>45658</v>
+      </c>
+      <c r="C22" t="s">
+        <v>14</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0.559322033898305</v>
+      </c>
+      <c r="E22" t="n">
+        <v>33</v>
+      </c>
+      <c r="F22" t="n">
+        <v>59</v>
+      </c>
+      <c r="G22" t="s">
+        <v>8</v>
+      </c>
+      <c r="H22" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>55</v>
+      </c>
+      <c r="B23" s="1" t="n">
+        <v>45748</v>
+      </c>
+      <c r="C23" t="s">
+        <v>14</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0.605442176870749</v>
+      </c>
+      <c r="E23" t="n">
+        <v>178</v>
+      </c>
+      <c r="F23" t="n">
+        <v>294</v>
+      </c>
+      <c r="G23" t="s">
+        <v>8</v>
+      </c>
+      <c r="H23" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>55</v>
+      </c>
+      <c r="B24" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C24" t="s">
+        <v>14</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0.716216216216211</v>
+      </c>
+      <c r="E24" t="n">
+        <v>265</v>
+      </c>
+      <c r="F24" t="n">
+        <v>370</v>
+      </c>
+      <c r="G24" t="s">
+        <v>8</v>
+      </c>
+      <c r="H24" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>55</v>
+      </c>
+      <c r="B25" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C25" t="s">
+        <v>14</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0.652931854199681</v>
+      </c>
+      <c r="E25" t="n">
+        <v>412</v>
+      </c>
+      <c r="F25" t="n">
+        <v>631</v>
+      </c>
+      <c r="G25" t="s">
+        <v>8</v>
+      </c>
+      <c r="H25" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>55</v>
+      </c>
+      <c r="B26" s="1" t="n">
+        <v>45658</v>
+      </c>
+      <c r="C26" t="s">
+        <v>15</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0.474576271186441</v>
+      </c>
+      <c r="E26" t="n">
+        <v>28</v>
+      </c>
+      <c r="F26" t="n">
+        <v>59</v>
+      </c>
+      <c r="G26" t="s">
+        <v>16</v>
+      </c>
+      <c r="H26" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>55</v>
+      </c>
+      <c r="B27" s="1" t="n">
+        <v>45748</v>
+      </c>
+      <c r="C27" t="s">
+        <v>15</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0.506802721088436</v>
+      </c>
+      <c r="E27" t="n">
+        <v>149</v>
+      </c>
+      <c r="F27" t="n">
+        <v>294</v>
+      </c>
+      <c r="G27" t="s">
+        <v>16</v>
+      </c>
+      <c r="H27" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>55</v>
+      </c>
+      <c r="B28" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C28" t="s">
+        <v>15</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0.464864864864863</v>
+      </c>
+      <c r="E28" t="n">
+        <v>172</v>
+      </c>
+      <c r="F28" t="n">
+        <v>370</v>
+      </c>
+      <c r="G28" t="s">
+        <v>16</v>
+      </c>
+      <c r="H28" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>55</v>
+      </c>
+      <c r="B29" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C29" t="s">
+        <v>15</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0.491283676703647</v>
+      </c>
+      <c r="E29" t="n">
+        <v>310</v>
+      </c>
+      <c r="F29" t="n">
+        <v>631</v>
+      </c>
+      <c r="G29" t="s">
+        <v>16</v>
+      </c>
+      <c r="H29" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s">
+        <v>55</v>
+      </c>
+      <c r="B30" s="1" t="n">
+        <v>45658</v>
+      </c>
+      <c r="C30" t="s">
+        <v>17</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0.338983050847458</v>
+      </c>
+      <c r="E30" t="n">
+        <v>20</v>
+      </c>
+      <c r="F30" t="n">
+        <v>59</v>
+      </c>
+      <c r="G30" t="s">
+        <v>16</v>
+      </c>
+      <c r="H30" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s">
+        <v>55</v>
+      </c>
+      <c r="B31" s="1" t="n">
+        <v>45748</v>
+      </c>
+      <c r="C31" t="s">
+        <v>17</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0.343537414965987</v>
+      </c>
+      <c r="E31" t="n">
+        <v>101</v>
+      </c>
+      <c r="F31" t="n">
+        <v>294</v>
+      </c>
+      <c r="G31" t="s">
+        <v>16</v>
+      </c>
+      <c r="H31" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s">
+        <v>55</v>
+      </c>
+      <c r="B32" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C32" t="s">
+        <v>17</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0.354054054054053</v>
+      </c>
+      <c r="E32" t="n">
+        <v>131</v>
+      </c>
+      <c r="F32" t="n">
+        <v>370</v>
+      </c>
+      <c r="G32" t="s">
+        <v>16</v>
+      </c>
+      <c r="H32" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s">
+        <v>55</v>
+      </c>
+      <c r="B33" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C33" t="s">
+        <v>17</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0.354992076069732</v>
+      </c>
+      <c r="E33" t="n">
+        <v>224</v>
+      </c>
+      <c r="F33" t="n">
+        <v>631</v>
+      </c>
+      <c r="G33" t="s">
+        <v>16</v>
+      </c>
+      <c r="H33" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s">
+        <v>55</v>
+      </c>
+      <c r="B34" s="1" t="n">
+        <v>45658</v>
+      </c>
+      <c r="C34" t="s">
+        <v>18</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0.254237288135593</v>
+      </c>
+      <c r="E34" t="n">
+        <v>15</v>
+      </c>
+      <c r="F34" t="n">
+        <v>59</v>
+      </c>
+      <c r="G34" t="s">
+        <v>16</v>
+      </c>
+      <c r="H34" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s">
+        <v>55</v>
+      </c>
+      <c r="B35" s="1" t="n">
+        <v>45748</v>
+      </c>
+      <c r="C35" t="s">
+        <v>18</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0.289115646258504</v>
+      </c>
+      <c r="E35" t="n">
+        <v>85</v>
+      </c>
+      <c r="F35" t="n">
+        <v>294</v>
+      </c>
+      <c r="G35" t="s">
+        <v>16</v>
+      </c>
+      <c r="H35" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s">
+        <v>55</v>
+      </c>
+      <c r="B36" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C36" t="s">
+        <v>18</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0.286486486486486</v>
+      </c>
+      <c r="E36" t="n">
+        <v>106</v>
+      </c>
+      <c r="F36" t="n">
+        <v>370</v>
+      </c>
+      <c r="G36" t="s">
+        <v>16</v>
+      </c>
+      <c r="H36" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s">
+        <v>55</v>
+      </c>
+      <c r="B37" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C37" t="s">
+        <v>18</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0.320126782884312</v>
+      </c>
+      <c r="E37" t="n">
+        <v>202</v>
+      </c>
+      <c r="F37" t="n">
+        <v>631</v>
+      </c>
+      <c r="G37" t="s">
+        <v>16</v>
+      </c>
+      <c r="H37" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s">
+        <v>55</v>
+      </c>
+      <c r="B38" s="1" t="n">
+        <v>45658</v>
+      </c>
+      <c r="C38" t="s">
+        <v>19</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0.593220338983051</v>
+      </c>
+      <c r="E38" t="n">
+        <v>35</v>
+      </c>
+      <c r="F38" t="n">
+        <v>59</v>
+      </c>
+      <c r="G38" t="s">
+        <v>16</v>
+      </c>
+      <c r="H38" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s">
+        <v>55</v>
+      </c>
+      <c r="B39" s="1" t="n">
+        <v>45748</v>
+      </c>
+      <c r="C39" t="s">
+        <v>19</v>
+      </c>
+      <c r="D39" t="n">
+        <v>0.612244897959184</v>
+      </c>
+      <c r="E39" t="n">
+        <v>180</v>
+      </c>
+      <c r="F39" t="n">
+        <v>294</v>
+      </c>
+      <c r="G39" t="s">
+        <v>16</v>
+      </c>
+      <c r="H39" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s">
+        <v>55</v>
+      </c>
+      <c r="B40" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C40" t="s">
+        <v>19</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0.618918918918915</v>
+      </c>
+      <c r="E40" t="n">
+        <v>229</v>
+      </c>
+      <c r="F40" t="n">
+        <v>370</v>
+      </c>
+      <c r="G40" t="s">
+        <v>16</v>
+      </c>
+      <c r="H40" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s">
+        <v>55</v>
+      </c>
+      <c r="B41" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C41" t="s">
+        <v>19</v>
+      </c>
+      <c r="D41" t="n">
+        <v>0.602218700475435</v>
+      </c>
+      <c r="E41" t="n">
+        <v>380</v>
+      </c>
+      <c r="F41" t="n">
+        <v>631</v>
+      </c>
+      <c r="G41" t="s">
+        <v>16</v>
+      </c>
+      <c r="H41" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s">
+        <v>55</v>
+      </c>
+      <c r="B42" s="1" t="n">
+        <v>45658</v>
+      </c>
+      <c r="C42" t="s">
+        <v>20</v>
+      </c>
+      <c r="D42" t="n">
+        <v>0.423728813559322</v>
+      </c>
+      <c r="E42" t="n">
+        <v>25</v>
+      </c>
+      <c r="F42" t="n">
+        <v>59</v>
+      </c>
+      <c r="G42" t="s">
+        <v>16</v>
+      </c>
+      <c r="H42" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s">
+        <v>55</v>
+      </c>
+      <c r="B43" s="1" t="n">
+        <v>45748</v>
+      </c>
+      <c r="C43" t="s">
+        <v>20</v>
+      </c>
+      <c r="D43" t="n">
+        <v>0.479591836734694</v>
+      </c>
+      <c r="E43" t="n">
+        <v>141</v>
+      </c>
+      <c r="F43" t="n">
+        <v>294</v>
+      </c>
+      <c r="G43" t="s">
+        <v>16</v>
+      </c>
+      <c r="H43" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s">
+        <v>55</v>
+      </c>
+      <c r="B44" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C44" t="s">
+        <v>20</v>
+      </c>
+      <c r="D44" t="n">
+        <v>0.524324324324322</v>
+      </c>
+      <c r="E44" t="n">
+        <v>194</v>
+      </c>
+      <c r="F44" t="n">
+        <v>370</v>
+      </c>
+      <c r="G44" t="s">
+        <v>16</v>
+      </c>
+      <c r="H44" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s">
+        <v>55</v>
+      </c>
+      <c r="B45" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C45" t="s">
+        <v>20</v>
+      </c>
+      <c r="D45" t="n">
+        <v>0.508716323296357</v>
+      </c>
+      <c r="E45" t="n">
+        <v>321</v>
+      </c>
+      <c r="F45" t="n">
+        <v>631</v>
+      </c>
+      <c r="G45" t="s">
+        <v>16</v>
+      </c>
+      <c r="H45" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s">
+        <v>55</v>
+      </c>
+      <c r="B46" s="1" t="n">
+        <v>45658</v>
+      </c>
+      <c r="C46" t="s">
+        <v>21</v>
+      </c>
+      <c r="D46" t="n">
+        <v>0.491525423728814</v>
+      </c>
+      <c r="E46" t="n">
+        <v>29</v>
+      </c>
+      <c r="F46" t="n">
+        <v>59</v>
+      </c>
+      <c r="G46" t="s">
+        <v>16</v>
+      </c>
+      <c r="H46" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s">
+        <v>55</v>
+      </c>
+      <c r="B47" s="1" t="n">
+        <v>45748</v>
+      </c>
+      <c r="C47" t="s">
+        <v>21</v>
+      </c>
+      <c r="D47" t="n">
+        <v>0.540816326530613</v>
+      </c>
+      <c r="E47" t="n">
+        <v>159</v>
+      </c>
+      <c r="F47" t="n">
+        <v>294</v>
+      </c>
+      <c r="G47" t="s">
+        <v>16</v>
+      </c>
+      <c r="H47" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s">
+        <v>55</v>
+      </c>
+      <c r="B48" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C48" t="s">
+        <v>21</v>
+      </c>
+      <c r="D48" t="n">
+        <v>0.529729729729727</v>
+      </c>
+      <c r="E48" t="n">
+        <v>196</v>
+      </c>
+      <c r="F48" t="n">
+        <v>370</v>
+      </c>
+      <c r="G48" t="s">
+        <v>16</v>
+      </c>
+      <c r="H48" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s">
+        <v>55</v>
+      </c>
+      <c r="B49" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C49" t="s">
+        <v>21</v>
+      </c>
+      <c r="D49" t="n">
+        <v>0.559429477020603</v>
+      </c>
+      <c r="E49" t="n">
+        <v>353</v>
+      </c>
+      <c r="F49" t="n">
+        <v>631</v>
+      </c>
+      <c r="G49" t="s">
+        <v>16</v>
+      </c>
+      <c r="H49" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s">
+        <v>55</v>
+      </c>
+      <c r="B50" s="1" t="n">
+        <v>45658</v>
+      </c>
+      <c r="C50" t="s">
+        <v>22</v>
+      </c>
+      <c r="D50" t="n">
+        <v>0.474576271186441</v>
+      </c>
+      <c r="E50" t="n">
+        <v>28</v>
+      </c>
+      <c r="F50" t="n">
+        <v>59</v>
+      </c>
+      <c r="G50" t="s">
+        <v>16</v>
+      </c>
+      <c r="H50" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s">
+        <v>55</v>
+      </c>
+      <c r="B51" s="1" t="n">
+        <v>45748</v>
+      </c>
+      <c r="C51" t="s">
+        <v>22</v>
+      </c>
+      <c r="D51" t="n">
+        <v>0.510204081632654</v>
+      </c>
+      <c r="E51" t="n">
+        <v>150</v>
+      </c>
+      <c r="F51" t="n">
+        <v>294</v>
+      </c>
+      <c r="G51" t="s">
+        <v>16</v>
+      </c>
+      <c r="H51" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s">
+        <v>55</v>
+      </c>
+      <c r="B52" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C52" t="s">
+        <v>22</v>
+      </c>
+      <c r="D52" t="n">
+        <v>0.518918918918916</v>
+      </c>
+      <c r="E52" t="n">
+        <v>192</v>
+      </c>
+      <c r="F52" t="n">
+        <v>370</v>
+      </c>
+      <c r="G52" t="s">
+        <v>16</v>
+      </c>
+      <c r="H52" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s">
+        <v>55</v>
+      </c>
+      <c r="B53" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C53" t="s">
+        <v>22</v>
+      </c>
+      <c r="D53" t="n">
+        <v>0.472266244057054</v>
+      </c>
+      <c r="E53" t="n">
+        <v>298</v>
+      </c>
+      <c r="F53" t="n">
+        <v>631</v>
+      </c>
+      <c r="G53" t="s">
+        <v>16</v>
+      </c>
+      <c r="H53" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s">
+        <v>55</v>
+      </c>
+      <c r="B54" s="1" t="n">
+        <v>45658</v>
+      </c>
+      <c r="C54" t="s">
+        <v>23</v>
+      </c>
+      <c r="D54" t="n">
+        <v>0.355932203389831</v>
+      </c>
+      <c r="E54" t="n">
+        <v>21</v>
+      </c>
+      <c r="F54" t="n">
+        <v>59</v>
+      </c>
+      <c r="G54" t="s">
+        <v>16</v>
+      </c>
+      <c r="H54" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s">
+        <v>55</v>
+      </c>
+      <c r="B55" s="1" t="n">
+        <v>45748</v>
+      </c>
+      <c r="C55" t="s">
+        <v>23</v>
+      </c>
+      <c r="D55" t="n">
+        <v>0.479591836734694</v>
+      </c>
+      <c r="E55" t="n">
+        <v>141</v>
+      </c>
+      <c r="F55" t="n">
+        <v>294</v>
+      </c>
+      <c r="G55" t="s">
+        <v>16</v>
+      </c>
+      <c r="H55" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s">
+        <v>55</v>
+      </c>
+      <c r="B56" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C56" t="s">
+        <v>23</v>
+      </c>
+      <c r="D56" t="n">
+        <v>0.527027027027024</v>
+      </c>
+      <c r="E56" t="n">
+        <v>195</v>
+      </c>
+      <c r="F56" t="n">
+        <v>370</v>
+      </c>
+      <c r="G56" t="s">
+        <v>16</v>
+      </c>
+      <c r="H56" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s">
+        <v>55</v>
+      </c>
+      <c r="B57" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C57" t="s">
+        <v>23</v>
+      </c>
+      <c r="D57" t="n">
+        <v>0.541996830427893</v>
+      </c>
+      <c r="E57" t="n">
+        <v>342</v>
+      </c>
+      <c r="F57" t="n">
+        <v>631</v>
+      </c>
+      <c r="G57" t="s">
+        <v>16</v>
+      </c>
+      <c r="H57" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s">
+        <v>55</v>
+      </c>
+      <c r="B58" s="1" t="n">
+        <v>45658</v>
+      </c>
+      <c r="C58" t="s">
+        <v>24</v>
+      </c>
+      <c r="D58" t="n">
+        <v>0.457627118644068</v>
+      </c>
+      <c r="E58" t="n">
+        <v>27</v>
+      </c>
+      <c r="F58" t="n">
+        <v>59</v>
+      </c>
+      <c r="G58" t="s">
+        <v>16</v>
+      </c>
+      <c r="H58" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s">
+        <v>55</v>
+      </c>
+      <c r="B59" s="1" t="n">
+        <v>45748</v>
+      </c>
+      <c r="C59" t="s">
+        <v>24</v>
+      </c>
+      <c r="D59" t="n">
+        <v>0.425170068027211</v>
+      </c>
+      <c r="E59" t="n">
+        <v>125</v>
+      </c>
+      <c r="F59" t="n">
+        <v>294</v>
+      </c>
+      <c r="G59" t="s">
+        <v>16</v>
+      </c>
+      <c r="H59" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s">
+        <v>55</v>
+      </c>
+      <c r="B60" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C60" t="s">
+        <v>24</v>
+      </c>
+      <c r="D60" t="n">
+        <v>0.432432432432431</v>
+      </c>
+      <c r="E60" t="n">
+        <v>160</v>
+      </c>
+      <c r="F60" t="n">
+        <v>370</v>
+      </c>
+      <c r="G60" t="s">
+        <v>16</v>
+      </c>
+      <c r="H60" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s">
+        <v>55</v>
+      </c>
+      <c r="B61" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C61" t="s">
+        <v>24</v>
+      </c>
+      <c r="D61" t="n">
+        <v>0.454833597464344</v>
+      </c>
+      <c r="E61" t="n">
+        <v>287</v>
+      </c>
+      <c r="F61" t="n">
+        <v>631</v>
+      </c>
+      <c r="G61" t="s">
+        <v>16</v>
+      </c>
+      <c r="H61" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s">
+        <v>55</v>
+      </c>
+      <c r="B62" s="1" t="n">
+        <v>45658</v>
+      </c>
+      <c r="C62" t="s">
+        <v>25</v>
+      </c>
+      <c r="D62" t="n">
+        <v>0.406779661016949</v>
+      </c>
+      <c r="E62" t="n">
+        <v>24</v>
+      </c>
+      <c r="F62" t="n">
+        <v>59</v>
+      </c>
+      <c r="G62" t="s">
+        <v>16</v>
+      </c>
+      <c r="H62" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s">
+        <v>55</v>
+      </c>
+      <c r="B63" s="1" t="n">
+        <v>45748</v>
+      </c>
+      <c r="C63" t="s">
+        <v>25</v>
+      </c>
+      <c r="D63" t="n">
+        <v>0.503401360544218</v>
+      </c>
+      <c r="E63" t="n">
+        <v>148</v>
+      </c>
+      <c r="F63" t="n">
+        <v>294</v>
+      </c>
+      <c r="G63" t="s">
+        <v>16</v>
+      </c>
+      <c r="H63" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s">
+        <v>55</v>
+      </c>
+      <c r="B64" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C64" t="s">
+        <v>25</v>
+      </c>
+      <c r="D64" t="n">
+        <v>0.497297297297295</v>
+      </c>
+      <c r="E64" t="n">
+        <v>184</v>
+      </c>
+      <c r="F64" t="n">
+        <v>370</v>
+      </c>
+      <c r="G64" t="s">
+        <v>16</v>
+      </c>
+      <c r="H64" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s">
+        <v>55</v>
+      </c>
+      <c r="B65" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C65" t="s">
+        <v>25</v>
+      </c>
+      <c r="D65" t="n">
+        <v>0.503961965134709</v>
+      </c>
+      <c r="E65" t="n">
+        <v>318</v>
+      </c>
+      <c r="F65" t="n">
+        <v>631</v>
+      </c>
+      <c r="G65" t="s">
+        <v>16</v>
+      </c>
+      <c r="H65" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s">
+        <v>55</v>
+      </c>
+      <c r="B66" s="1" t="n">
+        <v>45658</v>
+      </c>
+      <c r="C66" t="s">
+        <v>26</v>
+      </c>
+      <c r="D66" t="n">
+        <v>0.491525423728814</v>
+      </c>
+      <c r="E66" t="n">
+        <v>29</v>
+      </c>
+      <c r="F66" t="n">
+        <v>59</v>
+      </c>
+      <c r="G66" t="s">
+        <v>16</v>
+      </c>
+      <c r="H66" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s">
+        <v>55</v>
+      </c>
+      <c r="B67" s="1" t="n">
+        <v>45748</v>
+      </c>
+      <c r="C67" t="s">
+        <v>26</v>
+      </c>
+      <c r="D67" t="n">
+        <v>0.57482993197279</v>
+      </c>
+      <c r="E67" t="n">
+        <v>169</v>
+      </c>
+      <c r="F67" t="n">
+        <v>294</v>
+      </c>
+      <c r="G67" t="s">
+        <v>16</v>
+      </c>
+      <c r="H67" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s">
+        <v>55</v>
+      </c>
+      <c r="B68" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C68" t="s">
+        <v>26</v>
+      </c>
+      <c r="D68" t="n">
+        <v>0.594594594594591</v>
+      </c>
+      <c r="E68" t="n">
+        <v>220</v>
+      </c>
+      <c r="F68" t="n">
+        <v>370</v>
+      </c>
+      <c r="G68" t="s">
+        <v>16</v>
+      </c>
+      <c r="H68" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s">
+        <v>55</v>
+      </c>
+      <c r="B69" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C69" t="s">
+        <v>26</v>
+      </c>
+      <c r="D69" t="n">
+        <v>0.610142630744849</v>
+      </c>
+      <c r="E69" t="n">
+        <v>385</v>
+      </c>
+      <c r="F69" t="n">
+        <v>631</v>
+      </c>
+      <c r="G69" t="s">
+        <v>16</v>
+      </c>
+      <c r="H69" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s">
+        <v>55</v>
+      </c>
+      <c r="B70" s="1" t="n">
+        <v>45658</v>
+      </c>
+      <c r="C70" t="s">
+        <v>27</v>
+      </c>
+      <c r="D70" t="n">
+        <v>0.372881355932204</v>
+      </c>
+      <c r="E70" t="n">
+        <v>22</v>
+      </c>
+      <c r="F70" t="n">
+        <v>59</v>
+      </c>
+      <c r="G70" t="s">
+        <v>16</v>
+      </c>
+      <c r="H70" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s">
+        <v>55</v>
+      </c>
+      <c r="B71" s="1" t="n">
+        <v>45748</v>
+      </c>
+      <c r="C71" t="s">
+        <v>27</v>
+      </c>
+      <c r="D71" t="n">
+        <v>0.493197278911565</v>
+      </c>
+      <c r="E71" t="n">
+        <v>145</v>
+      </c>
+      <c r="F71" t="n">
+        <v>294</v>
+      </c>
+      <c r="G71" t="s">
+        <v>16</v>
+      </c>
+      <c r="H71" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s">
+        <v>55</v>
+      </c>
+      <c r="B72" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C72" t="s">
+        <v>27</v>
+      </c>
+      <c r="D72" t="n">
+        <v>0.475675675675673</v>
+      </c>
+      <c r="E72" t="n">
+        <v>176</v>
+      </c>
+      <c r="F72" t="n">
+        <v>370</v>
+      </c>
+      <c r="G72" t="s">
+        <v>16</v>
+      </c>
+      <c r="H72" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s">
+        <v>55</v>
+      </c>
+      <c r="B73" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C73" t="s">
+        <v>27</v>
+      </c>
+      <c r="D73" t="n">
+        <v>0.507131537242474</v>
+      </c>
+      <c r="E73" t="n">
+        <v>320</v>
+      </c>
+      <c r="F73" t="n">
+        <v>631</v>
+      </c>
+      <c r="G73" t="s">
+        <v>16</v>
+      </c>
+      <c r="H73" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s">
+        <v>55</v>
+      </c>
+      <c r="B74" s="1" t="n">
+        <v>45658</v>
+      </c>
+      <c r="C74" t="s">
+        <v>28</v>
+      </c>
+      <c r="D74" t="n">
+        <v>0.457627118644068</v>
+      </c>
+      <c r="E74" t="n">
+        <v>27</v>
+      </c>
+      <c r="F74" t="n">
+        <v>59</v>
+      </c>
+      <c r="G74" t="s">
+        <v>16</v>
+      </c>
+      <c r="H74" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s">
+        <v>55</v>
+      </c>
+      <c r="B75" s="1" t="n">
+        <v>45748</v>
+      </c>
+      <c r="C75" t="s">
+        <v>28</v>
+      </c>
+      <c r="D75" t="n">
+        <v>0.469387755102041</v>
+      </c>
+      <c r="E75" t="n">
+        <v>138</v>
+      </c>
+      <c r="F75" t="n">
+        <v>294</v>
+      </c>
+      <c r="G75" t="s">
+        <v>16</v>
+      </c>
+      <c r="H75" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s">
+        <v>55</v>
+      </c>
+      <c r="B76" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C76" t="s">
+        <v>28</v>
+      </c>
+      <c r="D76" t="n">
+        <v>0.524324324324322</v>
+      </c>
+      <c r="E76" t="n">
+        <v>194</v>
+      </c>
+      <c r="F76" t="n">
+        <v>370</v>
+      </c>
+      <c r="G76" t="s">
+        <v>16</v>
+      </c>
+      <c r="H76" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s">
+        <v>55</v>
+      </c>
+      <c r="B77" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C77" t="s">
+        <v>28</v>
+      </c>
+      <c r="D77" t="n">
+        <v>0.462757527733758</v>
+      </c>
+      <c r="E77" t="n">
+        <v>292</v>
+      </c>
+      <c r="F77" t="n">
+        <v>631</v>
+      </c>
+      <c r="G77" t="s">
+        <v>16</v>
+      </c>
+      <c r="H77" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s">
+        <v>55</v>
+      </c>
+      <c r="B78" s="1" t="n">
+        <v>45658</v>
+      </c>
+      <c r="C78" t="s">
+        <v>29</v>
+      </c>
+      <c r="D78" t="n">
+        <v>0.576271186440678</v>
+      </c>
+      <c r="E78" t="n">
+        <v>34</v>
+      </c>
+      <c r="F78" t="n">
+        <v>59</v>
+      </c>
+      <c r="G78" t="s">
+        <v>16</v>
+      </c>
+      <c r="H78" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="s">
+        <v>55</v>
+      </c>
+      <c r="B79" s="1" t="n">
+        <v>45748</v>
+      </c>
+      <c r="C79" t="s">
+        <v>29</v>
+      </c>
+      <c r="D79" t="n">
+        <v>0.523809523809524</v>
+      </c>
+      <c r="E79" t="n">
+        <v>154</v>
+      </c>
+      <c r="F79" t="n">
+        <v>294</v>
+      </c>
+      <c r="G79" t="s">
+        <v>16</v>
+      </c>
+      <c r="H79" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="s">
+        <v>55</v>
+      </c>
+      <c r="B80" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C80" t="s">
+        <v>29</v>
+      </c>
+      <c r="D80" t="n">
+        <v>0.551351351351348</v>
+      </c>
+      <c r="E80" t="n">
+        <v>204</v>
+      </c>
+      <c r="F80" t="n">
+        <v>370</v>
+      </c>
+      <c r="G80" t="s">
+        <v>16</v>
+      </c>
+      <c r="H80" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="s">
+        <v>55</v>
+      </c>
+      <c r="B81" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C81" t="s">
+        <v>29</v>
+      </c>
+      <c r="D81" t="n">
+        <v>0.592709984152139</v>
+      </c>
+      <c r="E81" t="n">
+        <v>374</v>
+      </c>
+      <c r="F81" t="n">
+        <v>631</v>
+      </c>
+      <c r="G81" t="s">
+        <v>16</v>
+      </c>
+      <c r="H81" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="s">
+        <v>55</v>
+      </c>
+      <c r="B82" s="1" t="n">
+        <v>45658</v>
+      </c>
+      <c r="C82" t="s">
+        <v>30</v>
+      </c>
+      <c r="D82" t="n">
+        <v>0.542372881355932</v>
+      </c>
+      <c r="E82" t="n">
+        <v>32</v>
+      </c>
+      <c r="F82" t="n">
+        <v>59</v>
+      </c>
+      <c r="G82" t="s">
+        <v>16</v>
+      </c>
+      <c r="H82" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="s">
+        <v>55</v>
+      </c>
+      <c r="B83" s="1" t="n">
+        <v>45748</v>
+      </c>
+      <c r="C83" t="s">
+        <v>30</v>
+      </c>
+      <c r="D83" t="n">
+        <v>0.482993197278912</v>
+      </c>
+      <c r="E83" t="n">
+        <v>142</v>
+      </c>
+      <c r="F83" t="n">
+        <v>294</v>
+      </c>
+      <c r="G83" t="s">
+        <v>16</v>
+      </c>
+      <c r="H83" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="s">
+        <v>55</v>
+      </c>
+      <c r="B84" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C84" t="s">
+        <v>30</v>
+      </c>
+      <c r="D84" t="n">
+        <v>0.481081081081079</v>
+      </c>
+      <c r="E84" t="n">
+        <v>178</v>
+      </c>
+      <c r="F84" t="n">
+        <v>370</v>
+      </c>
+      <c r="G84" t="s">
+        <v>16</v>
+      </c>
+      <c r="H84" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="s">
+        <v>55</v>
+      </c>
+      <c r="B85" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C85" t="s">
+        <v>30</v>
+      </c>
+      <c r="D85" t="n">
+        <v>0.513470681458005</v>
+      </c>
+      <c r="E85" t="n">
+        <v>324</v>
+      </c>
+      <c r="F85" t="n">
+        <v>631</v>
+      </c>
+      <c r="G85" t="s">
+        <v>16</v>
+      </c>
+      <c r="H85" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="s">
+        <v>55</v>
+      </c>
+      <c r="B86" s="1" t="n">
+        <v>45658</v>
+      </c>
+      <c r="C86" t="s">
+        <v>31</v>
+      </c>
+      <c r="D86" t="n">
+        <v>0.406779661016949</v>
+      </c>
+      <c r="E86" t="n">
+        <v>24</v>
+      </c>
+      <c r="F86" t="n">
+        <v>59</v>
+      </c>
+      <c r="G86" t="s">
+        <v>32</v>
+      </c>
+      <c r="H86" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="s">
+        <v>55</v>
+      </c>
+      <c r="B87" s="1" t="n">
+        <v>45748</v>
+      </c>
+      <c r="C87" t="s">
+        <v>31</v>
+      </c>
+      <c r="D87" t="n">
+        <v>0.551020408163266</v>
+      </c>
+      <c r="E87" t="n">
+        <v>162</v>
+      </c>
+      <c r="F87" t="n">
+        <v>294</v>
+      </c>
+      <c r="G87" t="s">
+        <v>32</v>
+      </c>
+      <c r="H87" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="s">
+        <v>55</v>
+      </c>
+      <c r="B88" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C88" t="s">
+        <v>31</v>
+      </c>
+      <c r="D88" t="n">
+        <v>0.516216216216213</v>
+      </c>
+      <c r="E88" t="n">
+        <v>191</v>
+      </c>
+      <c r="F88" t="n">
+        <v>370</v>
+      </c>
+      <c r="G88" t="s">
+        <v>32</v>
+      </c>
+      <c r="H88" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="s">
+        <v>55</v>
+      </c>
+      <c r="B89" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C89" t="s">
+        <v>31</v>
+      </c>
+      <c r="D89" t="n">
+        <v>0.515055467511888</v>
+      </c>
+      <c r="E89" t="n">
+        <v>325</v>
+      </c>
+      <c r="F89" t="n">
+        <v>631</v>
+      </c>
+      <c r="G89" t="s">
+        <v>32</v>
+      </c>
+      <c r="H89" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="s">
+        <v>55</v>
+      </c>
+      <c r="B90" s="1" t="n">
+        <v>45658</v>
+      </c>
+      <c r="C90" t="s">
+        <v>33</v>
+      </c>
+      <c r="D90" t="n">
+        <v>0.440677966101695</v>
+      </c>
+      <c r="E90" t="n">
+        <v>26</v>
+      </c>
+      <c r="F90" t="n">
+        <v>59</v>
+      </c>
+      <c r="G90" t="s">
+        <v>32</v>
+      </c>
+      <c r="H90" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="s">
+        <v>55</v>
+      </c>
+      <c r="B91" s="1" t="n">
+        <v>45748</v>
+      </c>
+      <c r="C91" t="s">
+        <v>33</v>
+      </c>
+      <c r="D91" t="n">
+        <v>0.503401360544218</v>
+      </c>
+      <c r="E91" t="n">
+        <v>148</v>
+      </c>
+      <c r="F91" t="n">
+        <v>294</v>
+      </c>
+      <c r="G91" t="s">
+        <v>32</v>
+      </c>
+      <c r="H91" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="s">
+        <v>55</v>
+      </c>
+      <c r="B92" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C92" t="s">
+        <v>33</v>
+      </c>
+      <c r="D92" t="n">
+        <v>0.486486486486484</v>
+      </c>
+      <c r="E92" t="n">
+        <v>180</v>
+      </c>
+      <c r="F92" t="n">
+        <v>370</v>
+      </c>
+      <c r="G92" t="s">
+        <v>32</v>
+      </c>
+      <c r="H92" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="s">
+        <v>55</v>
+      </c>
+      <c r="B93" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C93" t="s">
+        <v>33</v>
+      </c>
+      <c r="D93" t="n">
+        <v>0.494453248811413</v>
+      </c>
+      <c r="E93" t="n">
+        <v>312</v>
+      </c>
+      <c r="F93" t="n">
+        <v>631</v>
+      </c>
+      <c r="G93" t="s">
+        <v>32</v>
+      </c>
+      <c r="H93" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="s">
+        <v>55</v>
+      </c>
+      <c r="B94" s="1" t="n">
+        <v>45658</v>
+      </c>
+      <c r="C94" t="s">
+        <v>34</v>
+      </c>
+      <c r="D94" t="n">
+        <v>0.508474576271187</v>
+      </c>
+      <c r="E94" t="n">
+        <v>30</v>
+      </c>
+      <c r="F94" t="n">
+        <v>59</v>
+      </c>
+      <c r="G94" t="s">
+        <v>32</v>
+      </c>
+      <c r="H94" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="s">
+        <v>55</v>
+      </c>
+      <c r="B95" s="1" t="n">
+        <v>45748</v>
+      </c>
+      <c r="C95" t="s">
+        <v>34</v>
+      </c>
+      <c r="D95" t="n">
+        <v>0.537414965986395</v>
+      </c>
+      <c r="E95" t="n">
+        <v>158</v>
+      </c>
+      <c r="F95" t="n">
+        <v>294</v>
+      </c>
+      <c r="G95" t="s">
+        <v>32</v>
+      </c>
+      <c r="H95" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="s">
+        <v>55</v>
+      </c>
+      <c r="B96" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C96" t="s">
+        <v>34</v>
+      </c>
+      <c r="D96" t="n">
+        <v>0.589189189189186</v>
+      </c>
+      <c r="E96" t="n">
+        <v>218</v>
+      </c>
+      <c r="F96" t="n">
+        <v>370</v>
+      </c>
+      <c r="G96" t="s">
+        <v>32</v>
+      </c>
+      <c r="H96" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="s">
+        <v>55</v>
+      </c>
+      <c r="B97" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C97" t="s">
+        <v>34</v>
+      </c>
+      <c r="D97" t="n">
+        <v>0.553090332805072</v>
+      </c>
+      <c r="E97" t="n">
+        <v>349</v>
+      </c>
+      <c r="F97" t="n">
+        <v>631</v>
+      </c>
+      <c r="G97" t="s">
+        <v>32</v>
+      </c>
+      <c r="H97" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="s">
+        <v>55</v>
+      </c>
+      <c r="B98" s="1" t="n">
+        <v>45658</v>
+      </c>
+      <c r="C98" t="s">
+        <v>35</v>
+      </c>
+      <c r="D98" t="n">
+        <v>0.559322033898305</v>
+      </c>
+      <c r="E98" t="n">
+        <v>33</v>
+      </c>
+      <c r="F98" t="n">
+        <v>59</v>
+      </c>
+      <c r="G98" t="s">
+        <v>32</v>
+      </c>
+      <c r="H98" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="s">
+        <v>55</v>
+      </c>
+      <c r="B99" s="1" t="n">
+        <v>45748</v>
+      </c>
+      <c r="C99" t="s">
+        <v>35</v>
+      </c>
+      <c r="D99" t="n">
+        <v>0.534013605442177</v>
+      </c>
+      <c r="E99" t="n">
+        <v>157</v>
+      </c>
+      <c r="F99" t="n">
+        <v>294</v>
+      </c>
+      <c r="G99" t="s">
+        <v>32</v>
+      </c>
+      <c r="H99" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="s">
+        <v>55</v>
+      </c>
+      <c r="B100" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C100" t="s">
+        <v>35</v>
+      </c>
+      <c r="D100" t="n">
+        <v>0.554054054054051</v>
+      </c>
+      <c r="E100" t="n">
+        <v>205</v>
+      </c>
+      <c r="F100" t="n">
+        <v>370</v>
+      </c>
+      <c r="G100" t="s">
+        <v>32</v>
+      </c>
+      <c r="H100" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="s">
+        <v>55</v>
+      </c>
+      <c r="B101" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C101" t="s">
+        <v>35</v>
+      </c>
+      <c r="D101" t="n">
+        <v>0.564183835182251</v>
+      </c>
+      <c r="E101" t="n">
+        <v>356</v>
+      </c>
+      <c r="F101" t="n">
+        <v>631</v>
+      </c>
+      <c r="G101" t="s">
+        <v>32</v>
+      </c>
+      <c r="H101" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="s">
+        <v>55</v>
+      </c>
+      <c r="B102" s="1" t="n">
+        <v>45658</v>
+      </c>
+      <c r="C102" t="s">
+        <v>36</v>
+      </c>
+      <c r="D102" t="n">
+        <v>0.474576271186441</v>
+      </c>
+      <c r="E102" t="n">
+        <v>28</v>
+      </c>
+      <c r="F102" t="n">
+        <v>59</v>
+      </c>
+      <c r="G102" t="s">
+        <v>32</v>
+      </c>
+      <c r="H102" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="s">
+        <v>55</v>
+      </c>
+      <c r="B103" s="1" t="n">
+        <v>45748</v>
+      </c>
+      <c r="C103" t="s">
+        <v>36</v>
+      </c>
+      <c r="D103" t="n">
+        <v>0.465986394557824</v>
+      </c>
+      <c r="E103" t="n">
+        <v>137</v>
+      </c>
+      <c r="F103" t="n">
+        <v>294</v>
+      </c>
+      <c r="G103" t="s">
+        <v>32</v>
+      </c>
+      <c r="H103" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="s">
+        <v>55</v>
+      </c>
+      <c r="B104" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C104" t="s">
+        <v>36</v>
+      </c>
+      <c r="D104" t="n">
+        <v>0.456756756756755</v>
+      </c>
+      <c r="E104" t="n">
+        <v>169</v>
+      </c>
+      <c r="F104" t="n">
+        <v>370</v>
+      </c>
+      <c r="G104" t="s">
+        <v>32</v>
+      </c>
+      <c r="H104" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="s">
+        <v>55</v>
+      </c>
+      <c r="B105" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C105" t="s">
+        <v>36</v>
+      </c>
+      <c r="D105" t="n">
+        <v>0.49286846275753</v>
+      </c>
+      <c r="E105" t="n">
+        <v>311</v>
+      </c>
+      <c r="F105" t="n">
+        <v>631</v>
+      </c>
+      <c r="G105" t="s">
+        <v>32</v>
+      </c>
+      <c r="H105" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="s">
+        <v>55</v>
+      </c>
+      <c r="B106" s="1" t="n">
+        <v>45658</v>
+      </c>
+      <c r="C106" t="s">
+        <v>37</v>
+      </c>
+      <c r="D106" t="n">
+        <v>0.491525423728814</v>
+      </c>
+      <c r="E106" t="n">
+        <v>29</v>
+      </c>
+      <c r="F106" t="n">
+        <v>59</v>
+      </c>
+      <c r="G106" t="s">
+        <v>32</v>
+      </c>
+      <c r="H106" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="s">
+        <v>55</v>
+      </c>
+      <c r="B107" s="1" t="n">
+        <v>45748</v>
+      </c>
+      <c r="C107" t="s">
+        <v>37</v>
+      </c>
+      <c r="D107" t="n">
+        <v>0.517006802721089</v>
+      </c>
+      <c r="E107" t="n">
+        <v>152</v>
+      </c>
+      <c r="F107" t="n">
+        <v>294</v>
+      </c>
+      <c r="G107" t="s">
+        <v>32</v>
+      </c>
+      <c r="H107" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="s">
+        <v>55</v>
+      </c>
+      <c r="B108" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C108" t="s">
+        <v>37</v>
+      </c>
+      <c r="D108" t="n">
+        <v>0.5027027027027</v>
+      </c>
+      <c r="E108" t="n">
+        <v>186</v>
+      </c>
+      <c r="F108" t="n">
+        <v>370</v>
+      </c>
+      <c r="G108" t="s">
+        <v>32</v>
+      </c>
+      <c r="H108" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="s">
+        <v>55</v>
+      </c>
+      <c r="B109" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C109" t="s">
+        <v>37</v>
+      </c>
+      <c r="D109" t="n">
+        <v>0.507131537242474</v>
+      </c>
+      <c r="E109" t="n">
+        <v>320</v>
+      </c>
+      <c r="F109" t="n">
+        <v>631</v>
+      </c>
+      <c r="G109" t="s">
+        <v>32</v>
+      </c>
+      <c r="H109" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="s">
+        <v>55</v>
+      </c>
+      <c r="B110" s="1" t="n">
+        <v>45658</v>
+      </c>
+      <c r="C110" t="s">
+        <v>38</v>
+      </c>
+      <c r="D110" t="n">
+        <v>0.457627118644068</v>
+      </c>
+      <c r="E110" t="n">
+        <v>27</v>
+      </c>
+      <c r="F110" t="n">
+        <v>59</v>
+      </c>
+      <c r="G110" t="s">
+        <v>32</v>
+      </c>
+      <c r="H110" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="s">
+        <v>55</v>
+      </c>
+      <c r="B111" s="1" t="n">
+        <v>45748</v>
+      </c>
+      <c r="C111" t="s">
+        <v>38</v>
+      </c>
+      <c r="D111" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E111" t="n">
+        <v>147</v>
+      </c>
+      <c r="F111" t="n">
+        <v>294</v>
+      </c>
+      <c r="G111" t="s">
+        <v>32</v>
+      </c>
+      <c r="H111" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="s">
+        <v>55</v>
+      </c>
+      <c r="B112" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C112" t="s">
+        <v>38</v>
+      </c>
+      <c r="D112" t="n">
+        <v>0.510810810810808</v>
+      </c>
+      <c r="E112" t="n">
+        <v>189</v>
+      </c>
+      <c r="F112" t="n">
+        <v>370</v>
+      </c>
+      <c r="G112" t="s">
+        <v>32</v>
+      </c>
+      <c r="H112" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="s">
+        <v>55</v>
+      </c>
+      <c r="B113" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C113" t="s">
+        <v>38</v>
+      </c>
+      <c r="D113" t="n">
+        <v>0.49286846275753</v>
+      </c>
+      <c r="E113" t="n">
+        <v>311</v>
+      </c>
+      <c r="F113" t="n">
+        <v>631</v>
+      </c>
+      <c r="G113" t="s">
+        <v>32</v>
+      </c>
+      <c r="H113" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="s">
+        <v>55</v>
+      </c>
+      <c r="B114" s="1" t="n">
+        <v>45658</v>
+      </c>
+      <c r="C114" t="s">
+        <v>39</v>
+      </c>
+      <c r="D114" t="n">
+        <v>0.355932203389831</v>
+      </c>
+      <c r="E114" t="n">
+        <v>21</v>
+      </c>
+      <c r="F114" t="n">
+        <v>59</v>
+      </c>
+      <c r="G114" t="s">
+        <v>32</v>
+      </c>
+      <c r="H114" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="s">
+        <v>55</v>
+      </c>
+      <c r="B115" s="1" t="n">
+        <v>45748</v>
+      </c>
+      <c r="C115" t="s">
+        <v>39</v>
+      </c>
+      <c r="D115" t="n">
+        <v>0.374149659863946</v>
+      </c>
+      <c r="E115" t="n">
+        <v>110</v>
+      </c>
+      <c r="F115" t="n">
+        <v>294</v>
+      </c>
+      <c r="G115" t="s">
+        <v>32</v>
+      </c>
+      <c r="H115" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="s">
+        <v>55</v>
+      </c>
+      <c r="B116" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C116" t="s">
+        <v>39</v>
+      </c>
+      <c r="D116" t="n">
+        <v>0.329729729729729</v>
+      </c>
+      <c r="E116" t="n">
+        <v>122</v>
+      </c>
+      <c r="F116" t="n">
+        <v>370</v>
+      </c>
+      <c r="G116" t="s">
+        <v>32</v>
+      </c>
+      <c r="H116" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="s">
+        <v>55</v>
+      </c>
+      <c r="B117" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C117" t="s">
+        <v>39</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.351822503961966</v>
+      </c>
+      <c r="E117" t="n">
+        <v>222</v>
+      </c>
+      <c r="F117" t="n">
+        <v>631</v>
+      </c>
+      <c r="G117" t="s">
+        <v>32</v>
+      </c>
+      <c r="H117" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="s">
+        <v>55</v>
+      </c>
+      <c r="B118" s="1" t="n">
+        <v>45658</v>
+      </c>
+      <c r="C118" t="s">
+        <v>40</v>
+      </c>
+      <c r="D118" t="n">
+        <v>0.559322033898305</v>
+      </c>
+      <c r="E118" t="n">
+        <v>33</v>
+      </c>
+      <c r="F118" t="n">
+        <v>59</v>
+      </c>
+      <c r="G118" t="s">
+        <v>32</v>
+      </c>
+      <c r="H118" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="s">
+        <v>55</v>
+      </c>
+      <c r="B119" s="1" t="n">
+        <v>45748</v>
+      </c>
+      <c r="C119" t="s">
+        <v>40</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.568027210884354</v>
+      </c>
+      <c r="E119" t="n">
+        <v>167</v>
+      </c>
+      <c r="F119" t="n">
+        <v>294</v>
+      </c>
+      <c r="G119" t="s">
+        <v>32</v>
+      </c>
+      <c r="H119" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="s">
+        <v>55</v>
+      </c>
+      <c r="B120" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C120" t="s">
+        <v>40</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.581081081081078</v>
+      </c>
+      <c r="E120" t="n">
+        <v>215</v>
+      </c>
+      <c r="F120" t="n">
+        <v>370</v>
+      </c>
+      <c r="G120" t="s">
+        <v>32</v>
+      </c>
+      <c r="H120" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="s">
+        <v>55</v>
+      </c>
+      <c r="B121" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C121" t="s">
+        <v>40</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.591125198098256</v>
+      </c>
+      <c r="E121" t="n">
+        <v>373</v>
+      </c>
+      <c r="F121" t="n">
+        <v>631</v>
+      </c>
+      <c r="G121" t="s">
+        <v>32</v>
+      </c>
+      <c r="H121" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="s">
+        <v>55</v>
+      </c>
+      <c r="B122" s="1" t="n">
+        <v>45658</v>
+      </c>
+      <c r="C122" t="s">
+        <v>41</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.440677966101695</v>
+      </c>
+      <c r="E122" t="n">
+        <v>26</v>
+      </c>
+      <c r="F122" t="n">
+        <v>59</v>
+      </c>
+      <c r="G122" t="s">
+        <v>32</v>
+      </c>
+      <c r="H122" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="s">
+        <v>55</v>
+      </c>
+      <c r="B123" s="1" t="n">
+        <v>45748</v>
+      </c>
+      <c r="C123" t="s">
+        <v>41</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.45578231292517</v>
+      </c>
+      <c r="E123" t="n">
+        <v>134</v>
+      </c>
+      <c r="F123" t="n">
+        <v>294</v>
+      </c>
+      <c r="G123" t="s">
+        <v>32</v>
+      </c>
+      <c r="H123" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="s">
+        <v>55</v>
+      </c>
+      <c r="B124" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C124" t="s">
+        <v>41</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.518918918918916</v>
+      </c>
+      <c r="E124" t="n">
+        <v>192</v>
+      </c>
+      <c r="F124" t="n">
+        <v>370</v>
+      </c>
+      <c r="G124" t="s">
+        <v>32</v>
+      </c>
+      <c r="H124" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="s">
+        <v>55</v>
+      </c>
+      <c r="B125" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C125" t="s">
+        <v>41</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.505546751188592</v>
+      </c>
+      <c r="E125" t="n">
+        <v>319</v>
+      </c>
+      <c r="F125" t="n">
+        <v>631</v>
+      </c>
+      <c r="G125" t="s">
+        <v>32</v>
+      </c>
+      <c r="H125" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="s">
+        <v>55</v>
+      </c>
+      <c r="B126" s="1" t="n">
+        <v>45658</v>
+      </c>
+      <c r="C126" t="s">
+        <v>42</v>
+      </c>
+      <c r="D126" t="n">
+        <v>0.627118644067796</v>
+      </c>
+      <c r="E126" t="n">
+        <v>37</v>
+      </c>
+      <c r="F126" t="n">
+        <v>59</v>
+      </c>
+      <c r="G126" t="s">
+        <v>32</v>
+      </c>
+      <c r="H126" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="s">
+        <v>55</v>
+      </c>
+      <c r="B127" s="1" t="n">
+        <v>45748</v>
+      </c>
+      <c r="C127" t="s">
+        <v>42</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.58843537414966</v>
+      </c>
+      <c r="E127" t="n">
+        <v>173</v>
+      </c>
+      <c r="F127" t="n">
+        <v>294</v>
+      </c>
+      <c r="G127" t="s">
+        <v>32</v>
+      </c>
+      <c r="H127" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="s">
+        <v>55</v>
+      </c>
+      <c r="B128" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C128" t="s">
+        <v>42</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.54324324324324</v>
+      </c>
+      <c r="E128" t="n">
+        <v>201</v>
+      </c>
+      <c r="F128" t="n">
+        <v>370</v>
+      </c>
+      <c r="G128" t="s">
+        <v>32</v>
+      </c>
+      <c r="H128" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="s">
+        <v>55</v>
+      </c>
+      <c r="B129" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C129" t="s">
+        <v>42</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.565768621236133</v>
+      </c>
+      <c r="E129" t="n">
+        <v>357</v>
+      </c>
+      <c r="F129" t="n">
+        <v>631</v>
+      </c>
+      <c r="G129" t="s">
+        <v>32</v>
+      </c>
+      <c r="H129" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="s">
+        <v>55</v>
+      </c>
+      <c r="B130" s="1" t="n">
+        <v>45658</v>
+      </c>
+      <c r="C130" t="s">
+        <v>43</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.610169491525424</v>
+      </c>
+      <c r="E130" t="n">
+        <v>36</v>
+      </c>
+      <c r="F130" t="n">
+        <v>59</v>
+      </c>
+      <c r="G130" t="s">
+        <v>32</v>
+      </c>
+      <c r="H130" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="s">
+        <v>55</v>
+      </c>
+      <c r="B131" s="1" t="n">
+        <v>45748</v>
+      </c>
+      <c r="C131" t="s">
+        <v>43</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.622448979591837</v>
+      </c>
+      <c r="E131" t="n">
+        <v>183</v>
+      </c>
+      <c r="F131" t="n">
+        <v>294</v>
+      </c>
+      <c r="G131" t="s">
+        <v>32</v>
+      </c>
+      <c r="H131" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="s">
+        <v>55</v>
+      </c>
+      <c r="B132" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C132" t="s">
+        <v>43</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.594594594594591</v>
+      </c>
+      <c r="E132" t="n">
+        <v>220</v>
+      </c>
+      <c r="F132" t="n">
+        <v>370</v>
+      </c>
+      <c r="G132" t="s">
+        <v>32</v>
+      </c>
+      <c r="H132" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="s">
+        <v>55</v>
+      </c>
+      <c r="B133" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C133" t="s">
+        <v>43</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.600633914421552</v>
+      </c>
+      <c r="E133" t="n">
+        <v>379</v>
+      </c>
+      <c r="F133" t="n">
+        <v>631</v>
+      </c>
+      <c r="G133" t="s">
+        <v>32</v>
+      </c>
+      <c r="H133" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="s">
+        <v>55</v>
+      </c>
+      <c r="B134" s="1" t="n">
+        <v>45658</v>
+      </c>
+      <c r="C134" t="s">
+        <v>44</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.474576271186441</v>
+      </c>
+      <c r="E134" t="n">
+        <v>28</v>
+      </c>
+      <c r="F134" t="n">
+        <v>59</v>
+      </c>
+      <c r="G134" t="s">
+        <v>32</v>
+      </c>
+      <c r="H134" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="s">
+        <v>55</v>
+      </c>
+      <c r="B135" s="1" t="n">
+        <v>45748</v>
+      </c>
+      <c r="C135" t="s">
+        <v>44</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.517006802721089</v>
+      </c>
+      <c r="E135" t="n">
+        <v>152</v>
+      </c>
+      <c r="F135" t="n">
+        <v>294</v>
+      </c>
+      <c r="G135" t="s">
+        <v>32</v>
+      </c>
+      <c r="H135" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="s">
+        <v>55</v>
+      </c>
+      <c r="B136" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C136" t="s">
+        <v>44</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.537837837837835</v>
+      </c>
+      <c r="E136" t="n">
+        <v>199</v>
+      </c>
+      <c r="F136" t="n">
+        <v>370</v>
+      </c>
+      <c r="G136" t="s">
+        <v>32</v>
+      </c>
+      <c r="H136" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="s">
+        <v>55</v>
+      </c>
+      <c r="B137" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C137" t="s">
+        <v>44</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.51664025356577</v>
+      </c>
+      <c r="E137" t="n">
+        <v>326</v>
+      </c>
+      <c r="F137" t="n">
+        <v>631</v>
+      </c>
+      <c r="G137" t="s">
+        <v>32</v>
+      </c>
+      <c r="H137" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="s">
+        <v>55</v>
+      </c>
+      <c r="B138" s="1" t="n">
+        <v>45658</v>
+      </c>
+      <c r="C138" t="s">
+        <v>45</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.644067796610169</v>
+      </c>
+      <c r="E138" t="n">
+        <v>38</v>
+      </c>
+      <c r="F138" t="n">
+        <v>59</v>
+      </c>
+      <c r="G138" t="s">
+        <v>32</v>
+      </c>
+      <c r="H138" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="s">
+        <v>55</v>
+      </c>
+      <c r="B139" s="1" t="n">
+        <v>45748</v>
+      </c>
+      <c r="C139" t="s">
+        <v>45</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.608843537414967</v>
+      </c>
+      <c r="E139" t="n">
+        <v>179</v>
+      </c>
+      <c r="F139" t="n">
+        <v>294</v>
+      </c>
+      <c r="G139" t="s">
+        <v>32</v>
+      </c>
+      <c r="H139" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="s">
+        <v>55</v>
+      </c>
+      <c r="B140" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C140" t="s">
+        <v>45</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.608108108108104</v>
+      </c>
+      <c r="E140" t="n">
+        <v>225</v>
+      </c>
+      <c r="F140" t="n">
+        <v>370</v>
+      </c>
+      <c r="G140" t="s">
+        <v>32</v>
+      </c>
+      <c r="H140" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="s">
+        <v>55</v>
+      </c>
+      <c r="B141" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C141" t="s">
+        <v>45</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.597464342313787</v>
+      </c>
+      <c r="E141" t="n">
+        <v>377</v>
+      </c>
+      <c r="F141" t="n">
+        <v>631</v>
+      </c>
+      <c r="G141" t="s">
+        <v>32</v>
+      </c>
+      <c r="H141" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="s">
+        <v>55</v>
+      </c>
+      <c r="B142" s="1" t="n">
+        <v>45658</v>
+      </c>
+      <c r="C142" t="s">
+        <v>46</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.338983050847458</v>
+      </c>
+      <c r="E142" t="n">
+        <v>20</v>
+      </c>
+      <c r="F142" t="n">
+        <v>59</v>
+      </c>
+      <c r="G142" t="s">
+        <v>32</v>
+      </c>
+      <c r="H142" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="s">
+        <v>55</v>
+      </c>
+      <c r="B143" s="1" t="n">
+        <v>45748</v>
+      </c>
+      <c r="C143" t="s">
+        <v>46</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.45578231292517</v>
+      </c>
+      <c r="E143" t="n">
+        <v>134</v>
+      </c>
+      <c r="F143" t="n">
+        <v>294</v>
+      </c>
+      <c r="G143" t="s">
+        <v>32</v>
+      </c>
+      <c r="H143" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="s">
+        <v>55</v>
+      </c>
+      <c r="B144" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C144" t="s">
+        <v>46</v>
+      </c>
+      <c r="D144" t="n">
+        <v>0.424324324324323</v>
+      </c>
+      <c r="E144" t="n">
+        <v>157</v>
+      </c>
+      <c r="F144" t="n">
+        <v>370</v>
+      </c>
+      <c r="G144" t="s">
+        <v>32</v>
+      </c>
+      <c r="H144" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="s">
+        <v>55</v>
+      </c>
+      <c r="B145" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C145" t="s">
+        <v>46</v>
+      </c>
+      <c r="D145" t="n">
+        <v>0.434231378763869</v>
+      </c>
+      <c r="E145" t="n">
+        <v>274</v>
+      </c>
+      <c r="F145" t="n">
+        <v>631</v>
+      </c>
+      <c r="G145" t="s">
+        <v>32</v>
+      </c>
+      <c r="H145" t="s">
+        <v>9</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
 </file>